--- a/results/05_transient_transcription_output/501/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/501/original_transcribed_data.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5698
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
@@ -758,7 +758,7 @@
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -770,7 +770,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -785,25 +785,25 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>323</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">43
+</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2468
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
@@ -826,7 +826,7 @@
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -838,13 +838,13 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
@@ -863,7 +863,9 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>08561435132</t>
+          <t xml:space="preserve">27
+2
+</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -874,7 +876,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -886,11 +888,15 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="n"/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">84
@@ -917,13 +923,13 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">355
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -941,7 +947,7 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
@@ -953,7 +959,7 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">572
 </t>
         </is>
       </c>
@@ -965,7 +971,7 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">088
+          <t xml:space="preserve">410
 </t>
         </is>
       </c>
@@ -989,14 +995,13 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>808</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1014,12 +1019,14 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>08561435132</t>
+          <t xml:space="preserve">27
+2
+</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">339
+          <t xml:space="preserve">3321
 </t>
         </is>
       </c>
@@ -1029,10 +1036,15 @@
 </t>
         </is>
       </c>
-      <c r="F6" s="3" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2319
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -1050,7 +1062,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1062,31 +1074,30 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>94887</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">400
+          <t xml:space="preserve">408
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -1104,7 +1115,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -1128,12 +1139,13 @@
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t xml:space="preserve">135
+</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -1163,18 +1175,18 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5836
+          <t xml:space="preserve">536
 </t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>352</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -1192,7 +1204,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1210,7 +1222,8 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -1227,13 +1240,13 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">350
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -1245,7 +1258,7 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">347
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
@@ -1287,13 +1300,13 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1318,36 +1331,32 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>425</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">344
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">034
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
@@ -1355,31 +1364,32 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">022
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">1921
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11108
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">365
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t xml:space="preserve">265
+</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -1402,7 +1412,7 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -1420,18 +1430,17 @@
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>15</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -1460,27 +1469,38 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660
-</t>
+          <t>26562</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>611</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>614</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n"/>
+          <t xml:space="preserve">533
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1114
+</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="n"/>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2262
+411464141
+</t>
+        </is>
+      </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">442
@@ -1495,26 +1515,26 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">671
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="n"/>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1838
+          <t xml:space="preserve">1830
 </t>
         </is>
       </c>
@@ -1526,13 +1546,13 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650
+          <t xml:space="preserve">16850
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -1545,7 +1565,7 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2241
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
@@ -1557,25 +1577,25 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">389
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1062
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
@@ -1594,17 +1614,19 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>331</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1633,39 +1655,35 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>326</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366
-</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t xml:space="preserve">366
+</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="n"/>
       <c r="Q10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">330
@@ -1680,48 +1698,48 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>55</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">448
+</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1382
+</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1841
+</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">448
-</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="W10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="X10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1502
 </t>
         </is>
       </c>
@@ -1740,13 +1758,13 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4279
+          <t xml:space="preserve">4229
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -1763,24 +1781,23 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>411</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="K11" s="3" t="n"/>
@@ -1799,17 +1816,18 @@
       <c r="N11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2
+8
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1828,13 +1846,13 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">2290
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -1846,19 +1864,19 @@
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1023
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
+          <t xml:space="preserve">4240
 </t>
         </is>
       </c>
@@ -1878,19 +1896,19 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 6
+          <t xml:space="preserve">567
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 317
+          <t xml:space="preserve">7119
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -1902,13 +1920,14 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">1929
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">148
+</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1925,7 +1944,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -1943,7 +1962,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -1961,18 +1980,18 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3108
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>44</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -1984,35 +2003,32 @@
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>048</t>
-        </is>
-      </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="n"/>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">45
+76
 </t>
         </is>
       </c>
@@ -2031,7 +2047,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6013
+          <t xml:space="preserve">613
 </t>
         </is>
       </c>
@@ -2043,7 +2059,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -2061,7 +2077,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -2097,7 +2113,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -2109,7 +2125,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">396
 </t>
         </is>
       </c>
@@ -2121,7 +2137,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -2139,20 +2155,19 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">440
+          <t xml:space="preserve">496
 </t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">2872
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
@@ -2163,7 +2178,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">408
 </t>
         </is>
       </c>
@@ -2195,7 +2210,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -2213,7 +2228,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -2231,13 +2246,13 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">020
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -2249,13 +2264,13 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -2267,19 +2282,19 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3803
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -2291,20 +2306,18 @@
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>412</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
@@ -2343,19 +2356,18 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1795
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
@@ -2378,7 +2390,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2390,13 +2402,13 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -2420,13 +2432,13 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -2444,7 +2456,7 @@
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -2468,7 +2480,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
@@ -2487,25 +2499,24 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95721
+          <t xml:space="preserve">25777
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11896
+          <t xml:space="preserve">526
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>81</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2522,49 +2533,56 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">353
+</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">362
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">1811
+14
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
+          <t xml:space="preserve">8223
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="n"/>
+          <t xml:space="preserve">443222
+181909191
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2125
+          <t xml:space="preserve">21215
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">622
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1547
+          <t xml:space="preserve">547
 </t>
         </is>
       </c>
@@ -2581,11 +2599,17 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="U16" s="3" t="n"/>
+          <t xml:space="preserve">8206
+</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+7918949
+</t>
+        </is>
+      </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1315
@@ -2594,7 +2618,7 @@
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -2606,13 +2630,13 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1458
+          <t xml:space="preserve">1488
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -2631,25 +2655,25 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -2661,41 +2685,41 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="n"/>
+          <t xml:space="preserve">1134
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="n"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">425
@@ -2704,63 +2728,65 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">0624
 </t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">3609
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>44</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">723
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>963</t>
+          <t xml:space="preserve">263
+</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">7
+</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">849
+          <t xml:space="preserve">449
 </t>
         </is>
       </c>
@@ -2779,50 +2805,47 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521
+          <t xml:space="preserve">521
+2
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>349</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 7
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="n"/>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>164</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">80
+</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="n"/>
       <c r="L18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">135
@@ -2831,30 +2854,30 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
@@ -2865,19 +2888,18 @@
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">376
+          <t xml:space="preserve">3726
 </t>
         </is>
       </c>
@@ -2907,7 +2929,7 @@
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -2926,17 +2948,23 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3264
+          <t xml:space="preserve">268
+2975
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n"/>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">229
@@ -2951,7 +2979,8 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>164</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -2967,7 +2996,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2982,15 +3011,10 @@
           <t>26</t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
+      <c r="N19" s="3" t="n"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
+          <t xml:space="preserve">608
 </t>
         </is>
       </c>
@@ -3002,12 +3026,13 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>391</t>
+          <t xml:space="preserve">320
+</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -3025,30 +3050,29 @@
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>962</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>61</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -3066,13 +3090,15 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5429
-</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">446466240
+212
+79719019
+</t>
+        </is>
+      </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">123
@@ -3081,8 +3107,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -3099,7 +3124,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -3111,7 +3136,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -3123,19 +3148,19 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -3147,13 +3172,13 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>106</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -3170,23 +3195,27 @@
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">414
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
-        </is>
-      </c>
-      <c r="X20" s="3" t="n"/>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">320
@@ -3209,14 +3238,19 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5429
-</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="n"/>
+          <t xml:space="preserve">5422
+</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">309
+</t>
+        </is>
+      </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -3227,90 +3261,89 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1231
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">63
+</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1256
+</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">307
+</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4920
-</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">283
-</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">122
+</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -3328,7 +3361,8 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -3339,7 +3373,7 @@
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>146</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3357,12 +3391,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>341</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -3373,14 +3407,12 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>435</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3391,19 +3423,20 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">200
+</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -3414,19 +3447,19 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">115
+</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
@@ -3437,7 +3470,7 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -3454,7 +3487,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -3466,7 +3499,8 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t>982</t>
+          <t xml:space="preserve">220
+</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
@@ -3477,7 +3511,7 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -3501,38 +3535,35 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25475
-</t>
-        </is>
-      </c>
+      <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">603
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>261</t>
+          <t xml:space="preserve">868
+</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">44255
+82947
 </t>
         </is>
       </c>
@@ -3544,11 +3575,15 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
-</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="n"/>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -3556,35 +3591,35 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2720
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>736</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -3595,19 +3630,18 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">2920
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
@@ -3625,11 +3659,16 @@
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
-</t>
-        </is>
-      </c>
-      <c r="Z23" s="3" t="n"/>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1921
+</t>
+        </is>
+      </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3645,7 +3684,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>50321</t>
+          <t>50261</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3656,30 +3695,31 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1784
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -3691,48 +3731,46 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">503
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">546
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t xml:space="preserve">83
+</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1544
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -3755,7 +3793,7 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -3773,13 +3811,14 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>166</t>
+          <t xml:space="preserve">225
+</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3797,31 +3836,31 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">4555
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -3833,11 +3872,15 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="n"/>
+          <t xml:space="preserve">61
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="K25" s="3" t="n"/>
       <c r="L25" s="3" t="inlineStr">
         <is>
@@ -3847,14 +3890,19 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="n"/>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9
+</t>
+        </is>
+      </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">400
+          <t xml:space="preserve">4008
 </t>
         </is>
       </c>
@@ -3866,13 +3914,13 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t xml:space="preserve">5
+</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -3884,18 +3932,21 @@
       <c r="T25" s="3" t="n"/>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t>888</t>
+          <t xml:space="preserve">21
+2
+</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 6 11558
+          <t xml:space="preserve">182
+171111
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3907,8 +3958,7 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">455
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Z25" s="3" t="n"/>
@@ -3939,37 +3989,41 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2448
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="n"/>
+          <t xml:space="preserve">723
+</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">1089
 </t>
         </is>
       </c>
@@ -3981,19 +4035,19 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">020
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
@@ -4017,7 +4071,7 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -4029,28 +4083,30 @@
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>328234</t>
+          <t xml:space="preserve">8
+</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">2664
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">1494
+</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4070,52 +4126,57 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5501
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820
+          <t xml:space="preserve">22858
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16816
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
-</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="n"/>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">163
@@ -4130,19 +4191,19 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">985
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13220
+          <t xml:space="preserve">5280
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -4160,7 +4221,7 @@
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
@@ -4172,34 +4233,36 @@
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>42</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>96</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t>266</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">262
+309
 </t>
         </is>
       </c>
@@ -4224,7 +4287,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>334</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -4235,7 +4298,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -4247,25 +4310,25 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -4277,25 +4340,25 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
+          <t xml:space="preserve">4280
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -4307,53 +4370,53 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1660
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>434</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>132</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">262
+309
 </t>
         </is>
       </c>
@@ -4372,20 +4435,17 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6249
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -4402,12 +4462,13 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">204
+</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -4418,7 +4479,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -4436,13 +4497,13 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">413
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
@@ -4460,23 +4521,26 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="n"/>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">277
@@ -4517,13 +4581,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6249
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15616
+          <t xml:space="preserve">1416
 </t>
         </is>
       </c>
@@ -4535,37 +4598,37 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">370
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">358
+          <t xml:space="preserve">558
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4577,36 +4640,36 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>63</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2329
+          <t xml:space="preserve">2323
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
+          <t xml:space="preserve">512
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
@@ -4617,12 +4680,13 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t xml:space="preserve">90
+</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11941
+          <t xml:space="preserve">1941
 </t>
         </is>
       </c>
@@ -4634,19 +4698,19 @@
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
@@ -4666,8 +4730,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2364
-</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -4678,29 +4741,30 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t xml:space="preserve">50
+</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -4712,7 +4776,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">1929
 </t>
         </is>
       </c>
@@ -4741,34 +4805,28 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1551
-</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1424
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="T31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">826
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">6
+</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="n"/>
       <c r="U31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">388
@@ -4795,7 +4853,7 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4818,12 +4876,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
+      <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">338
@@ -4832,7 +4885,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -4844,36 +4897,31 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="n"/>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K32" s="3" t="n"/>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4908,44 +4956,45 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="T32" s="3" t="n"/>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">285
+</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="n"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -4959,21 +5008,15 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
+      <c r="C33" s="3" t="n"/>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>04444</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -4991,7 +5034,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>71</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -5002,13 +5045,13 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">358
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -5020,24 +5063,25 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">57
+</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1418
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -5049,25 +5093,25 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1847
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1062
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
+          <t xml:space="preserve">834
 </t>
         </is>
       </c>
@@ -5079,19 +5123,18 @@
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>445</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Z33" s="3" t="n"/>
@@ -5116,7 +5159,8 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>321</t>
+          <t xml:space="preserve">312
+</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -5145,7 +5189,7 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -5163,12 +5207,13 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5192,18 +5237,19 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">134
+</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -5233,19 +5279,20 @@
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">116
+178
 </t>
         </is>
       </c>
@@ -5264,19 +5311,18 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4379
+          <t xml:space="preserve">4339
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
+          <t>501</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0856
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -5294,7 +5340,7 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -5306,7 +5352,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -5324,20 +5370,25 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="n"/>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -5361,46 +5412,40 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">550
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
+          <t xml:space="preserve">334
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
-      <c r="Z35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="n"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -5416,13 +5461,13 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
@@ -5440,7 +5485,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -5458,13 +5503,12 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
-</t>
+          <t>442</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -5479,21 +5523,16 @@
 </t>
         </is>
       </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -5511,7 +5550,7 @@
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5523,13 +5562,13 @@
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
@@ -5541,13 +5580,13 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Z36" s="3" t="n"/>
@@ -5564,57 +5603,50 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2222
-</t>
-        </is>
-      </c>
+      <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1516
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">424
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>416</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K37" s="3" t="n"/>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">8219
 </t>
         </is>
       </c>
@@ -5624,21 +5656,16 @@
 </t>
         </is>
       </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3898
+          <t xml:space="preserve">598
 </t>
         </is>
       </c>
@@ -5650,18 +5677,18 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">478
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">341
 </t>
         </is>
       </c>
@@ -5678,22 +5705,26 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
+          <t xml:space="preserve">790
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>492</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
-</t>
-        </is>
-      </c>
-      <c r="Z37" s="3" t="n"/>
+          <t>1831</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">962
+</t>
+        </is>
+      </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -5714,7 +5745,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">1856
 </t>
         </is>
       </c>
@@ -5726,7 +5757,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
@@ -5738,7 +5769,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">558
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -5750,7 +5781,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13010
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
@@ -5768,12 +5799,13 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>132</t>
+          <t xml:space="preserve">532
+</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">478
 </t>
         </is>
       </c>
@@ -5785,19 +5817,19 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">598
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">1335
 </t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">1485
 </t>
         </is>
       </c>
@@ -5809,37 +5841,38 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1510
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
@@ -5863,50 +5896,55 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>54441</t>
+          <t>54444</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2821
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>512</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>614</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="n"/>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
@@ -5915,13 +5953,13 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1060004</t>
+          <t>406</t>
         </is>
       </c>
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
@@ -5951,13 +5989,13 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -5969,8 +6007,7 @@
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
@@ -5981,14 +6018,13 @@
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3964
+          <t xml:space="preserve">364
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6006,13 +6042,14 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6171
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>303</t>
+          <t xml:space="preserve">292
+</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -6035,14 +6072,13 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>512</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -6052,16 +6088,11 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
-</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1162
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="n"/>
       <c r="M40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">102
@@ -6070,12 +6101,12 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>948</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
@@ -6093,18 +6124,19 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">100
+</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8224
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -6128,19 +6160,19 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -6159,13 +6191,13 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -6176,31 +6208,31 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -6212,90 +6244,90 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">520
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">360
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">150
+</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">1975
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8289
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2236
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -6314,18 +6346,21 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">224
+4811
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>313</t>
+          <t xml:space="preserve">314
+</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>462</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -6342,13 +6377,13 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1530
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -6360,37 +6395,37 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">2020
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6402,54 +6437,54 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>455</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1655
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -6468,20 +6503,19 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3240
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -6492,37 +6526,36 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -6534,35 +6567,32 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">985
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t>762</t>
-        </is>
-      </c>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="n"/>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -6574,36 +6604,37 @@
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">1418
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">2853
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -6622,19 +6653,19 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">3605
 </t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
@@ -6646,7 +6677,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -6658,48 +6689,49 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">5815
+</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -6711,13 +6743,13 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1844
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">8898
 </t>
         </is>
       </c>
@@ -6729,25 +6761,25 @@
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -6759,7 +6791,7 @@
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -6778,19 +6810,19 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1857
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1501
 </t>
         </is>
       </c>
@@ -6808,19 +6840,19 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3560
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
@@ -6832,86 +6864,87 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2265
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>912</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8818
-</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="n"/>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>722</t>
+          <t xml:space="preserve">528
+</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t>752</t>
+          <t xml:space="preserve">212
+</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1865
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1841
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">22
+11
 </t>
         </is>
       </c>
@@ -6930,25 +6963,25 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518
+          <t xml:space="preserve">2322
 </t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">1877
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11399
+          <t xml:space="preserve">12321
 </t>
         </is>
       </c>
@@ -6956,88 +6989,84 @@
       <c r="H46" s="3" t="n"/>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">350
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">523
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n"/>
+          <t>5242</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0609
-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t xml:space="preserve">622
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="n"/>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">494
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>920</t>
+          <t xml:space="preserve">784
+</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1790
-</t>
+          <t>13321</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t xml:space="preserve">5128
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="n"/>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t xml:space="preserve">27
+</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">648
 </t>
         </is>
       </c>
@@ -7049,7 +7078,7 @@
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/501/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/501/original_transcribed_data.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
+          <t xml:space="preserve">15698
 </t>
         </is>
       </c>
@@ -737,15 +737,10 @@
           <t>335</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
+      <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -758,7 +753,7 @@
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1728
 </t>
         </is>
       </c>
@@ -770,12 +765,16 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="n"/>
-      <c r="M4" s="3" t="n"/>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
       <c r="N4" s="3" t="n"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
@@ -791,18 +790,19 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>323</t>
+          <t xml:space="preserve">2383
+</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -812,42 +812,12 @@
 </t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">468
-</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">322
-</t>
-        </is>
-      </c>
+      <c r="U4" s="3" t="n"/>
+      <c r="V4" s="3" t="n"/>
+      <c r="W4" s="3" t="n"/>
+      <c r="X4" s="3" t="n"/>
+      <c r="Y4" s="3" t="n"/>
+      <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -863,8 +833,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-2
+          <t xml:space="preserve">5127
 </t>
         </is>
       </c>
@@ -876,37 +845,36 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">2218
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>442</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -923,13 +891,13 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">355
+          <t xml:space="preserve">1655
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -941,67 +909,63 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
-</t>
-        </is>
-      </c>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="n"/>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
+          <t xml:space="preserve">1468
 </t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1284
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>808</t>
+          <t xml:space="preserve">322
+</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1019,14 +983,13 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-2
+          <t xml:space="preserve">15048
 </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3321
+          <t xml:space="preserve">3348
 </t>
         </is>
       </c>
@@ -1038,20 +1001,19 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1206231
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -1062,101 +1024,98 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">122
 </t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>94887</t>
-        </is>
-      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">1898
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">408
-</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11400
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="n"/>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">1327
 </t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">1152
 </t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">424
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>163</t>
+          <t xml:space="preserve">2012
+</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">2302
 </t>
         </is>
       </c>
@@ -1175,54 +1134,53 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">536
+          <t xml:space="preserve">5836
 </t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>353</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">1231
 </t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>461</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">0080
 </t>
         </is>
       </c>
@@ -1234,20 +1192,13 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1258,61 +1209,60 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">397
+          <t xml:space="preserve">347
 </t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
+          <t xml:space="preserve">1424
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">334
 </t>
         </is>
       </c>
@@ -1331,64 +1281,63 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n"/>
+          <t xml:space="preserve">4851
+</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">344
+</t>
+        </is>
+      </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">11510
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1272
-</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
+          <t xml:space="preserve">1227
+</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1910
+</t>
+        </is>
+      </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">022
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">71108
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">2365
 </t>
         </is>
       </c>
@@ -1406,52 +1355,54 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">1151
 </t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">1710
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">422
+          <t xml:space="preserve">9422
 </t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>451</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t xml:space="preserve">1153
+</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">1117
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t xml:space="preserve">867
+</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t>342</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1469,133 +1420,134 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>26562</t>
+          <t xml:space="preserve">26360
+</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>611</t>
+          <t xml:space="preserve">11697
+</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">533
-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>146</t>
+          <t xml:space="preserve">1164
+</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2262
-411464141
+          <t xml:space="preserve">391
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
+          <t xml:space="preserve">16442
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
+          <t xml:space="preserve">1684
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61
-</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="n"/>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">2587
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1830
+          <t xml:space="preserve">11830
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">497
+          <t xml:space="preserve">9497
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16850
+          <t xml:space="preserve">11690
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="S9" s="3" t="n"/>
+          <t xml:space="preserve">718
+</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1277
+</t>
+        </is>
+      </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">559
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">12241
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
+          <t xml:space="preserve">11397
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">1696
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">389
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">11862
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">11202
 </t>
         </is>
       </c>
@@ -1614,19 +1566,18 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">2312
 </t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
@@ -1638,52 +1589,59 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">1232
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">78
+</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>326</t>
+          <t xml:space="preserve">165
+</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
-</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="n"/>
+          <t xml:space="preserve">2366
+</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">330
@@ -1692,54 +1650,54 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t xml:space="preserve">88
+</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">448
+          <t xml:space="preserve">1448
 </t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">1279
 </t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1382
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1841
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
@@ -1758,36 +1716,31 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4229
+          <t xml:space="preserve">14278
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">300
+</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>421</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1797,7 +1750,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K11" s="3" t="n"/>
@@ -1809,35 +1762,35 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-8
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="n"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t xml:space="preserve">1130
+</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="n"/>
+          <t xml:space="preserve">9289
+</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11489
+</t>
+        </is>
+      </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">88
@@ -1846,40 +1799,25 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2290
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">1310
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4240
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1217
+</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="n"/>
+      <c r="X11" s="3" t="n"/>
+      <c r="Y11" s="3" t="n"/>
       <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1896,55 +1834,49 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
+          <t xml:space="preserve">20 6 1
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7119
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>448</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">1287
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1929
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1118
+</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -1956,42 +1888,42 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
+          <t xml:space="preserve">1530
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
+          <t xml:space="preserve">3118
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">144
+</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -2003,33 +1935,37 @@
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">1840
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>08</t>
-        </is>
-      </c>
-      <c r="Y12" s="3" t="n"/>
+          <t xml:space="preserve">1023
+</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">470
+</t>
+        </is>
+      </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-76
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2047,25 +1983,24 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">613
+          <t xml:space="preserve">16013
 </t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">343
-</t>
+          <t>343</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1154
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
@@ -2077,7 +2012,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
@@ -2089,13 +2024,13 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">1157
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -2107,82 +2042,81 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="n"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">12490
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">396
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
+          <t xml:space="preserve">8332
 </t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">496
+          <t xml:space="preserve">1440
 </t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2872
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>146</t>
+          <t xml:space="preserve">151
+</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">408
-</t>
-        </is>
-      </c>
-      <c r="Z13" s="3" t="n"/>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12654
+</t>
+        </is>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -2198,7 +2132,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4890
+          <t xml:space="preserve">14880
 </t>
         </is>
       </c>
@@ -2210,13 +2144,13 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
@@ -2228,7 +2162,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">1136
 </t>
         </is>
       </c>
@@ -2246,7 +2180,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">020
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -2258,79 +2192,67 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1120
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="n"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">1490
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2303
+</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="n"/>
+      <c r="S14" s="3" t="n"/>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2360
+</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="n"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">1144
+</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t xml:space="preserve">82
+</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="Z14" s="3" t="n"/>
+          <t xml:space="preserve">0208
+</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4312
+</t>
+        </is>
+      </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -2346,7 +2268,8 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>5524</t>
+          <t xml:space="preserve">18329
+</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -2356,29 +2279,31 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1795
+          <t xml:space="preserve">1020
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">1231
+</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t xml:space="preserve">102
+</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -2390,37 +2315,32 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">008
 </t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="n"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
@@ -2430,36 +2350,21 @@
 </t>
         </is>
       </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">69
-</t>
-        </is>
-      </c>
+      <c r="R15" s="3" t="n"/>
+      <c r="S15" s="3" t="n"/>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">1154
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
-</t>
-        </is>
-      </c>
-      <c r="V15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">3820
+</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="n"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">140
@@ -2468,20 +2373,19 @@
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">1234
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2499,78 +2403,73 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25777
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">526
+          <t xml:space="preserve">12916
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>151</t>
+          <t xml:space="preserve">27268
+</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>821</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">353
+          <t xml:space="preserve">973
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">562
+</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
-14
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8223
+          <t xml:space="preserve">1899
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">443222
-181909191
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">29529
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="n"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21215
+          <t xml:space="preserve">22120
 </t>
         </is>
       </c>
@@ -2582,13 +2481,14 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">547
+          <t xml:space="preserve">11547
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>236</t>
+          <t xml:space="preserve">10836
+</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -2599,44 +2499,43 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8206
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-7918949
+          <t xml:space="preserve">11882
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1315
+          <t xml:space="preserve">11310
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">483
+          <t xml:space="preserve">1483
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1488
+          <t xml:space="preserve">112458
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">11244
 </t>
         </is>
       </c>
@@ -2655,109 +2554,102 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">3154
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1236
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="N17" s="3" t="n"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
+          <t xml:space="preserve">9425
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0624
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3609
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>47</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
+          <t xml:space="preserve">1873
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">376
 </t>
         </is>
       </c>
@@ -2769,27 +2661,23 @@
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>2121</t>
-        </is>
-      </c>
-      <c r="Z17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">449
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2292
+</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="n"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2805,131 +2693,132 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-2
+          <t xml:space="preserve">5321
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>349</t>
+          <t xml:space="preserve">029
+</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="n"/>
+          <t xml:space="preserve">1124
+</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="n"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">76
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="n"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">166
+</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>29111</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t xml:space="preserve">1152
+</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t xml:space="preserve">1155
+</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3726
-</t>
-        </is>
-      </c>
-      <c r="V18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1404
+</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="n"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">11844
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
@@ -2948,20 +2837,19 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-2975
+          <t xml:space="preserve">3264
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">334
 </t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1123
 </t>
         </is>
       </c>
@@ -2979,48 +2867,45 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">87
+</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1926
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1135
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="n"/>
       <c r="N19" s="3" t="n"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">608
+          <t xml:space="preserve">1605
 </t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -3038,45 +2923,47 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="V19" s="3" t="inlineStr">
-        <is>
-          <t>962</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1414
+</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="n"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">1
+</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="Z19" s="3" t="n"/>
+          <t xml:space="preserve">1220
+</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">297
+</t>
+        </is>
+      </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -3090,18 +2977,16 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">446466240
-212
-79719019
-</t>
-        </is>
-      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n"/>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
@@ -3112,19 +2997,19 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -3136,37 +3021,35 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">1115
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">5220
 </t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -3178,7 +3061,8 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t xml:space="preserve">1146
+</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -3195,34 +3079,40 @@
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t xml:space="preserve">1222
+</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">11824
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
-        </is>
-      </c>
-      <c r="Z20" s="3" t="n"/>
+          <t xml:space="preserve">520
+</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -3244,66 +3134,61 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">1364
+</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
-</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1132
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">1775
 </t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">1115
 </t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
@@ -3314,7 +3199,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
@@ -3332,48 +3217,50 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">366
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t>146</t>
+          <t xml:space="preserve">246
+</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3391,39 +3278,42 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t xml:space="preserve">15363
+</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>348</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>435</t>
+          <t xml:space="preserve">12225
+</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>166</t>
+          <t xml:space="preserve">1166
+</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
@@ -3435,31 +3325,27 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">1010
 </t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1107
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="n"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t xml:space="preserve">510
+</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
@@ -3470,36 +3356,36 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">145
+</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">1849
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
+          <t xml:space="preserve">2390
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
@@ -3511,17 +3397,22 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="n"/>
+          <t xml:space="preserve">2163
+</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1262
+</t>
+        </is>
+      </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -3535,22 +3426,27 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2315
+</t>
+        </is>
+      </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">603
+          <t xml:space="preserve">1603
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">725
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">11171
 </t>
         </is>
       </c>
@@ -3562,8 +3458,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44255
-82947
+          <t xml:space="preserve">1600
 </t>
         </is>
       </c>
@@ -3575,51 +3470,56 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">33
+</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">7191
+</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">12120
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">1412
+</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">1544
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>736</t>
+          <t xml:space="preserve">135
+</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -3630,42 +3530,43 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t xml:space="preserve">1829
+</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920
+          <t xml:space="preserve">1872
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">13026
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
+          <t xml:space="preserve">1688
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">1428
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">11224
 </t>
         </is>
       </c>
@@ -3684,7 +3585,8 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>50261</t>
+          <t xml:space="preserve">3095
+</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3695,45 +3597,41 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1784
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1114
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -3742,25 +3640,20 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="n"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">546
+          <t xml:space="preserve">046
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -3770,7 +3663,7 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1147
 </t>
         </is>
       </c>
@@ -3781,19 +3674,19 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1872
+          <t xml:space="preserve">374
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
@@ -3805,19 +3698,19 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -3836,117 +3729,114 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4555
+          <t xml:space="preserve">4255
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2119
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>432</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1842
 </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="n"/>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1109
+</t>
+        </is>
+      </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="n"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4008
+          <t xml:space="preserve">1400
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">11140
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">83
-</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="n"/>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="n"/>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1202
+</t>
+        </is>
+      </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-2
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-171111
+          <t xml:space="preserve">1177
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
@@ -3958,10 +3848,16 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="n"/>
+          <t xml:space="preserve">14575
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11121
+</t>
+        </is>
+      </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -3989,12 +3885,13 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">1148
+</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">2225
 </t>
         </is>
       </c>
@@ -4006,48 +3903,43 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">102
+</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1089
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="n"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
@@ -4059,7 +3951,7 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
@@ -4071,46 +3963,46 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">334
 </t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2664
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="n"/>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="3" t="n"/>
+          <t xml:space="preserve">2270
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1250
+</t>
+        </is>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -4126,143 +4018,122 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">5501
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">1152
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22858
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">106
+</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">985
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="n"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5280
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="n"/>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">1374
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="inlineStr">
+          <t>48</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="n"/>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10266
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="Z27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-309
 </t>
         </is>
       </c>
@@ -4281,24 +4152,25 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6210
+          <t xml:space="preserve">16210
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>334</t>
+          <t xml:space="preserve">332
+</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
@@ -4310,13 +4182,12 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -4328,7 +4199,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -4340,83 +4211,84 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4280
+          <t xml:space="preserve">14280
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">11208
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">321
+</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">434
+</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1277
+</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1133
+</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">308
-</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">45
-</t>
-        </is>
-      </c>
-      <c r="T28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1660
-</t>
-        </is>
-      </c>
-      <c r="U28" s="3" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="V28" s="3" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="W28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">133
-</t>
-        </is>
-      </c>
-      <c r="X28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="Y28" s="3" t="inlineStr">
-        <is>
-          <t>1265</t>
-        </is>
-      </c>
-      <c r="Z28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-309
 </t>
         </is>
       </c>
@@ -4435,22 +4307,25 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">6249
+</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">344
+</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">1122
+</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
@@ -4462,24 +4337,25 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">127
+</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">1008
 </t>
         </is>
       </c>
@@ -4491,59 +4367,54 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">1413
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">3835
 </t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>456</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="n"/>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">1277
 </t>
         </is>
       </c>
@@ -4555,7 +4426,7 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -4565,7 +4436,12 @@
 </t>
         </is>
       </c>
-      <c r="Z29" s="3" t="n"/>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30682
+</t>
+        </is>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -4581,54 +4457,55 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">27819
+</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
+          <t xml:space="preserve">1616
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">7145
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">1871
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">1570
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
+          <t xml:space="preserve">3720
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">558
+          <t xml:space="preserve">1558
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
@@ -4640,53 +4517,50 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t xml:space="preserve">1306
+</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2323
+          <t xml:space="preserve">2223
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">512
+          <t xml:space="preserve">017
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">1531
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="S30" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+          <t xml:space="preserve">709
+</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="n"/>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">726
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1941
+          <t xml:space="preserve">81941
 </t>
         </is>
       </c>
@@ -4698,22 +4572,17 @@
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1668
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
-</t>
-        </is>
-      </c>
-      <c r="Y30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">283
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1120
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="n"/>
       <c r="Z30" s="3" t="n"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -4730,7 +4599,8 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t xml:space="preserve">2364
+</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -4741,62 +4611,48 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>489</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1929
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1112
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">164
 </t>
         </is>
       </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">506
-</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t>431</t>
-        </is>
-      </c>
+      <c r="M31" s="3" t="n"/>
+      <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">465
@@ -4805,28 +4661,29 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t xml:space="preserve">310
+</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1424
-</t>
-        </is>
-      </c>
-      <c r="S31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
-      </c>
-      <c r="T31" s="3" t="n"/>
+          <t xml:space="preserve">1142
+</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="n"/>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1145
+</t>
+        </is>
+      </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">388
@@ -4835,25 +4692,25 @@
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">2293
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
@@ -4876,7 +4733,12 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n"/>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0111
+</t>
+        </is>
+      </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">338
@@ -4885,52 +4747,56 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="n"/>
+          <t xml:space="preserve">112321
+</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="n"/>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="n"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">390
@@ -4943,58 +4809,46 @@
 </t>
         </is>
       </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
+      <c r="Q32" s="3" t="n"/>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1141
+</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="n"/>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="U32" s="3" t="inlineStr">
-        <is>
-          <t>4241</t>
-        </is>
-      </c>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="n"/>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">1283
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="n"/>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="n"/>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">319
+</t>
+        </is>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -5008,136 +4862,135 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n"/>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4487
+</t>
+        </is>
+      </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>04444</t>
+          <t xml:space="preserve">308
+</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">2229
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">1167
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t xml:space="preserve">111
+</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">358
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1410
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">336
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="n"/>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1062
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1147
+</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="n"/>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="U33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">834
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">303
+</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="n"/>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">12180
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>445</t>
+          <t xml:space="preserve">1135
+</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z33" s="3" t="n"/>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -5159,37 +5012,27 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1232
+</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -5201,7 +5044,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -5213,86 +5056,85 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">11160
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">522
+          <t xml:space="preserve">129522
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">0250
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">7190
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">1127
 </t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">116
-178
 </t>
         </is>
       </c>
@@ -5317,48 +5159,44 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>501</t>
+          <t xml:space="preserve">303
+</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1170
+</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1133
 </t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1285
 </t>
         </is>
       </c>
@@ -5370,37 +5208,32 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="n"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
@@ -5412,19 +5245,19 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
+          <t xml:space="preserve">2228
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
@@ -5442,10 +5275,15 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>431</t>
-        </is>
-      </c>
-      <c r="Z35" s="3" t="n"/>
+          <t xml:space="preserve">18398
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>4221</t>
+        </is>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -5461,135 +5299,132 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">3413
 </t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="n"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="n"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t xml:space="preserve">211
+</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>442</t>
+          <t xml:space="preserve">14
+</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1123
 </t>
         </is>
       </c>
       <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">1940
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">1136
 </t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z36" s="3" t="n"/>
+          <t xml:space="preserve">2188
+</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -5603,98 +5438,114 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n"/>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>9661</t>
+        </is>
+      </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">11816
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">1689
+</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">11102
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">827
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">424
+          <t xml:space="preserve">358
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>416</t>
+          <t xml:space="preserve">216
+</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="n"/>
+          <t xml:space="preserve">1010
+</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8219
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="n"/>
+          <t xml:space="preserve">1232
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">12402
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
-</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1335
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">17826
+</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1478
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">341
+          <t xml:space="preserve">11410
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">11342
+</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
@@ -5705,23 +5556,24 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">790
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>492</t>
+          <t xml:space="preserve">9498
+</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t xml:space="preserve">1812
+</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
@@ -5740,138 +5592,125 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>433</t>
+          <t xml:space="preserve">4433
+</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1856
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
-</t>
+          <t>428</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">827
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">21112
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">361
-</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">532
-</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">478
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="n"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">14180
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1335
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1485
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">2269
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">374
 </t>
         </is>
       </c>
@@ -5896,35 +5735,37 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>54444</t>
+          <t xml:space="preserve">3146
+</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t xml:space="preserve">1292
+</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1142
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">1800
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -5935,43 +5776,39 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>406</t>
+          <t xml:space="preserve">11102
+</t>
         </is>
       </c>
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
-</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="n"/>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -5989,42 +5826,39 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="V39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1224
+</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="n"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t xml:space="preserve">1150
+</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
+          <t xml:space="preserve">3964
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t xml:space="preserve">2266
+</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6042,71 +5876,77 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">6171
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">1262217
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>512</t>
+          <t xml:space="preserve">1086
+</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">183
+</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="n"/>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1162
+</t>
+        </is>
+      </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>948</t>
+          <t xml:space="preserve">92
+</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
@@ -6118,61 +5958,55 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
-</t>
-        </is>
-      </c>
-      <c r="V40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">7942
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="n"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1847
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">81206
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">12216
 </t>
         </is>
       </c>
@@ -6191,144 +6025,139 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">5875
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="n"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">93
+</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1975
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">2926
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1275
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">1288
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6346,145 +6175,137 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-4811
+          <t xml:space="preserve">4811
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1154
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1233
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1109
+</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="n"/>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">9209
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>464</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>455</t>
+          <t xml:space="preserve">1147
+</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">1928
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -6503,138 +6324,134 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">3540
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>164</t>
+          <t xml:space="preserve">164
+</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">2239
 </t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1041
 </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t xml:space="preserve">197
+</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="n"/>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="n"/>
+          <t xml:space="preserve">915
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="n"/>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1289
+</t>
+        </is>
+      </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1147
 </t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">2013
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1418
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2853
+          <t xml:space="preserve">19253
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">2461
 </t>
         </is>
       </c>
@@ -6653,133 +6470,122 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">2380
 </t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3605
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="n"/>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">6561
 </t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1909
+</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="n"/>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5815
+          <t xml:space="preserve">1440
 </t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1093
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">1147
 </t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">1122
 </t>
         </is>
       </c>
@@ -6791,7 +6597,7 @@
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1824
 </t>
         </is>
       </c>
@@ -6810,141 +6616,139 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">331029
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">118715
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1501
+          <t xml:space="preserve">1919
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">11221
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">822246
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
+          <t xml:space="preserve">15123
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">18222
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1110111
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">886
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18159
+</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="n"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">112265
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="n"/>
+          <t xml:space="preserve">10218
+</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1838
+</t>
+        </is>
+      </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">18369
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">528
+          <t xml:space="preserve">88886
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">214621
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1061
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">10987
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">12228
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-11
+          <t xml:space="preserve">11172
 </t>
         </is>
       </c>
@@ -6963,122 +6767,123 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2322
+          <t xml:space="preserve">5518
 </t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1877
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12321
-</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="n"/>
-      <c r="H46" s="3" t="n"/>
+          <t xml:space="preserve">1230
+</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1121
+</t>
+        </is>
+      </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">350
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>5242</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">622
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="n"/>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">1494
 </t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>13321</t>
+          <t xml:space="preserve">1288
+</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5128
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="n"/>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="inlineStr">
-        <is>
-          <t>7519</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="inlineStr">
+          <t xml:space="preserve">3908
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="n"/>
+      <c r="W46" s="3" t="n"/>
+      <c r="X46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">648
-</t>
-        </is>
-      </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/501/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/501/original_transcribed_data.xlsx
@@ -728,19 +728,25 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15698
+          <t xml:space="preserve">5628
 </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n"/>
+          <t xml:space="preserve">835
+</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">97
+</t>
+        </is>
+      </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -750,10 +756,15 @@
 </t>
         </is>
       </c>
-      <c r="H4" s="3" t="n"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -765,20 +776,31 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="n"/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="n"/>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">355
+          <t xml:space="preserve">345
 </t>
         </is>
       </c>
@@ -790,7 +812,7 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2383
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
@@ -802,7 +824,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
@@ -833,7 +855,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5127
+          <t xml:space="preserve">151 27 1
 </t>
         </is>
       </c>
@@ -845,59 +867,61 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2218
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">764
+</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>442</t>
+          <t xml:space="preserve">1129
+</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1655
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -909,7 +933,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -921,7 +945,7 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">1840
 </t>
         </is>
       </c>
@@ -931,40 +955,44 @@
 </t>
         </is>
       </c>
-      <c r="T5" s="3" t="n"/>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>04449</t>
+        </is>
+      </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1468
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1284
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">968
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">382
 </t>
         </is>
       </c>
@@ -983,13 +1011,13 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15048
+          <t xml:space="preserve">23048
 </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3348
+          <t xml:space="preserve">339
 </t>
         </is>
       </c>
@@ -1007,13 +1035,14 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206231
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t xml:space="preserve">75
+</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -1030,7 +1059,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1042,32 +1071,37 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1898
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11400
-</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="n"/>
+          <t xml:space="preserve">21098
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85
+</t>
+        </is>
+      </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1327
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -1085,7 +1119,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -1097,7 +1131,7 @@
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1642
 </t>
         </is>
       </c>
@@ -1109,13 +1143,13 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2302
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
@@ -1140,7 +1174,8 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>353</t>
+          <t xml:space="preserve">353
+</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1151,13 +1186,13 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -1175,12 +1210,13 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>461</t>
+          <t xml:space="preserve">169
+</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0080
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1192,13 +1228,20 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>546</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="n"/>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t xml:space="preserve">350
+</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1209,61 +1252,61 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">347
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">836
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">68
+</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1424
+          <t xml:space="preserve">017
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1281,63 +1324,74 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4851
+          <t xml:space="preserve">112851
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11510
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
-</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
+          <t xml:space="preserve">2828
+</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">812
+</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910
+          <t xml:space="preserve">0110
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">1161
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71108
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2365
+          <t xml:space="preserve">360
 </t>
         </is>
       </c>
@@ -1361,24 +1415,26 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1710
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">143
+</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422
+          <t xml:space="preserve">422
 </t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">2019
+</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
@@ -1389,22 +1445,17 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1117
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">867
-</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">110982
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="n"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1420,13 +1471,13 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26360
+          <t xml:space="preserve">26660
 </t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11697
+          <t xml:space="preserve">1697
 </t>
         </is>
       </c>
@@ -1436,7 +1487,12 @@
 </t>
         </is>
       </c>
-      <c r="F9" s="3" t="n"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14134
+</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1164
@@ -1445,55 +1501,61 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
+          <t xml:space="preserve">3291
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16442
+          <t xml:space="preserve">6142
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1684
+          <t xml:space="preserve">684
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="n"/>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">671
+</t>
+        </is>
+      </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">329
+</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2587
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11830
+          <t xml:space="preserve">1830
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9497
+          <t xml:space="preserve">487
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11690
+          <t xml:space="preserve">1690
 </t>
         </is>
       </c>
@@ -1505,7 +1567,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1277
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
@@ -1523,7 +1585,7 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11397
+          <t xml:space="preserve">1397
 </t>
         </is>
       </c>
@@ -1547,7 +1609,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11202
+          <t xml:space="preserve">11584
 </t>
         </is>
       </c>
@@ -1572,12 +1634,13 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t xml:space="preserve">229
+</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
+          <t xml:space="preserve">1872
 </t>
         </is>
       </c>
@@ -1589,19 +1652,19 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -1614,31 +1677,26 @@
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="n"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366
+          <t xml:space="preserve">366
 </t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -1650,12 +1708,13 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">144
+</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -1667,37 +1726,37 @@
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1448
+          <t xml:space="preserve">1948
 </t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -1716,44 +1775,58 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14278
+          <t xml:space="preserve">4279
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n"/>
+          <t xml:space="preserve">3080
+</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">838
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">139
+</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t xml:space="preserve">1148
+</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="n"/>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">182
@@ -1762,7 +1835,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">614
 </t>
         </is>
       </c>
@@ -1781,40 +1854,35 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9289
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11489
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">8220
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1310
-</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1217
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">8210
+</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="n"/>
       <c r="W11" s="3" t="n"/>
       <c r="X11" s="3" t="n"/>
       <c r="Y11" s="3" t="n"/>
@@ -1834,24 +1902,24 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20 6 1
+          <t xml:space="preserve">2067
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">517
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1287
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
@@ -1863,20 +1931,25 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n"/>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61
+</t>
+        </is>
+      </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -1894,36 +1967,37 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1530
+          <t xml:space="preserve">530
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">1100
+</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3118
+          <t xml:space="preserve">3108
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -1941,7 +2015,7 @@
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -1953,19 +2027,20 @@
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1023
+          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
+          <t xml:space="preserve">12170
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">18358
+</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -1983,30 +2058,31 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16013
+          <t xml:space="preserve">6013
 </t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>343</t>
+          <t xml:space="preserve">343
+</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">1594
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
@@ -2024,13 +2100,13 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1157
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2049,42 +2125,43 @@
       <c r="N13" s="3" t="n"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12490
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8332
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t xml:space="preserve">135
+</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1440
+          <t xml:space="preserve">440
 </t>
         </is>
       </c>
@@ -2096,25 +2173,25 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">1151
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">1021
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t xml:space="preserve">088
+</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12654
-</t>
+          <t>865</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2132,7 +2209,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14880
+          <t xml:space="preserve">4890
 </t>
         </is>
       </c>
@@ -2144,112 +2221,133 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1244
+</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1120
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">490
+</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">144
 </t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1136
-</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1120
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="n"/>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1490
-</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1144
-</t>
-        </is>
-      </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2303
-</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="n"/>
-      <c r="S14" s="3" t="n"/>
+          <t xml:space="preserve">303
+</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t xml:space="preserve">169
+</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2360
-</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="n"/>
+          <t xml:space="preserve">360
+</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">270
+</t>
+        </is>
+      </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">1812
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0208
+          <t xml:space="preserve">0808
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4312
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
@@ -2268,30 +2366,29 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18329
+          <t xml:space="preserve">2521
 </t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>343</t>
+          <t xml:space="preserve">315
+</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
-</t>
+          <t>933</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
@@ -2303,7 +2400,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -2315,43 +2412,58 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="n"/>
+          <t xml:space="preserve">1104
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9
+</t>
+        </is>
+      </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="n"/>
-      <c r="S15" s="3" t="n"/>
+          <t xml:space="preserve">3120
+</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1145
+</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1154
@@ -2360,14 +2472,18 @@
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3820
-</t>
-        </is>
-      </c>
-      <c r="V15" s="3" t="n"/>
+          <t xml:space="preserve">38208
+</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
@@ -2377,17 +2493,8 @@
 </t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1234
-</t>
-        </is>
-      </c>
-      <c r="Z15" s="3" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
+      <c r="Y15" s="3" t="n"/>
+      <c r="Z15" s="3" t="n"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>10</t>
@@ -2403,36 +2510,37 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">2371
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12916
+          <t xml:space="preserve">1823916
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27268
+          <t xml:space="preserve">2168
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>821</t>
+          <t xml:space="preserve">1182
+</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
+          <t xml:space="preserve">618
 </t>
         </is>
       </c>
@@ -2450,23 +2558,28 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1899
+          <t xml:space="preserve">1898
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29529
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="n"/>
+          <t xml:space="preserve">2028
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">22120
@@ -2481,13 +2594,13 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11547
+          <t xml:space="preserve">1547
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10836
+          <t xml:space="preserve">836
 </t>
         </is>
       </c>
@@ -2505,37 +2618,37 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11882
+          <t xml:space="preserve">1882
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11310
+          <t xml:space="preserve">1315
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1728
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1483
+          <t xml:space="preserve">483
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112458
+          <t xml:space="preserve">11438
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11244
+          <t xml:space="preserve">10244
 </t>
         </is>
       </c>
@@ -2560,31 +2673,31 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">3819
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">22316
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -2603,19 +2716,25 @@
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="n"/>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9425
+          <t xml:space="preserve">425
 </t>
         </is>
       </c>
@@ -2633,30 +2752,31 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1873
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>164</t>
+          <t xml:space="preserve">1164
+</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">376
+          <t xml:space="preserve">9816
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>9465</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
@@ -2673,11 +2793,16 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2292
-</t>
-        </is>
-      </c>
-      <c r="Z17" s="3" t="n"/>
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2693,25 +2818,24 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5321
+          <t xml:space="preserve">10321
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">029
+          <t xml:space="preserve">0229
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">827
 </t>
         </is>
       </c>
@@ -2723,18 +2847,18 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>134</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -2745,7 +2869,7 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -2755,7 +2879,12 @@
 </t>
         </is>
       </c>
-      <c r="N18" s="3" t="n"/>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">175
@@ -2764,18 +2893,19 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>29111</t>
+          <t xml:space="preserve">2804
+</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -2787,26 +2917,31 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404
-</t>
-        </is>
-      </c>
-      <c r="V18" s="3" t="n"/>
+          <t xml:space="preserve">404
+</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1081
+</t>
+        </is>
+      </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11844
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -2818,7 +2953,7 @@
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -2837,20 +2972,18 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3264
-</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
+          <t xml:space="preserve">354
 </t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -2879,7 +3012,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1926
+          <t xml:space="preserve">11206
 </t>
         </is>
       </c>
@@ -2891,21 +3024,31 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
-</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="n"/>
-      <c r="N19" s="3" t="n"/>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
+          <t xml:space="preserve">605
 </t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2917,7 +3060,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -2929,17 +3072,22 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1414
-</t>
-        </is>
-      </c>
-      <c r="V19" s="3" t="n"/>
+          <t xml:space="preserve">1614
+</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">129
@@ -2948,7 +3096,7 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
@@ -2960,7 +3108,7 @@
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -2979,31 +3127,37 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="n"/>
+          <t xml:space="preserve">93905
+</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">9149
 </t>
         </is>
       </c>
@@ -3015,41 +3169,42 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t xml:space="preserve">07
+</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>73</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -3061,7 +3216,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -3085,31 +3240,31 @@
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">16202
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11824
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
@@ -3128,55 +3283,61 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5422
+          <t xml:space="preserve">9422
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>302</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1364
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
-</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="n"/>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1775
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
@@ -3188,18 +3349,19 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>420</t>
+          <t xml:space="preserve">490
+</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -3217,13 +3379,13 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -3235,19 +3397,19 @@
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
+          <t xml:space="preserve">2863
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -3259,7 +3421,7 @@
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">2176
 </t>
         </is>
       </c>
@@ -3278,13 +3440,14 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15363
+          <t xml:space="preserve">5363
 </t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>348</t>
+          <t xml:space="preserve">318
+</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -3295,19 +3458,19 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12225
+          <t xml:space="preserve">2125
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -3325,23 +3488,28 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="n"/>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">510
@@ -3356,7 +3524,8 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t xml:space="preserve">313
+</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
@@ -3367,19 +3536,19 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2390
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
@@ -3391,7 +3560,7 @@
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
@@ -3403,13 +3572,13 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -3428,13 +3597,13 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2315
+          <t xml:space="preserve">25175
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1603
+          <t xml:space="preserve">1605
 </t>
         </is>
       </c>
@@ -3446,19 +3615,18 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11171
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">1868
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600
+          <t xml:space="preserve">1610
 </t>
         </is>
       </c>
@@ -3482,55 +3650,55 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7191
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">503
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12120
+          <t xml:space="preserve">2720
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412
+          <t xml:space="preserve">412
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1544
+          <t xml:space="preserve">1344
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">735
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
+          <t xml:space="preserve">566
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1829
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
@@ -3542,7 +3710,7 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13026
+          <t xml:space="preserve">1388
 </t>
         </is>
       </c>
@@ -3554,7 +3722,7 @@
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
+          <t xml:space="preserve">428
 </t>
         </is>
       </c>
@@ -3566,7 +3734,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11224
+          <t xml:space="preserve">11274
 </t>
         </is>
       </c>
@@ -3585,91 +3753,103 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3095
-</t>
+          <t>5435</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">046
+</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">346
+</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83
+</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">309
+</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">147
 </t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="n"/>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">046
-</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="R24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1147
-</t>
-        </is>
-      </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>73</t>
+          <t xml:space="preserve">73
+</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
@@ -3690,27 +3870,22 @@
 </t>
         </is>
       </c>
-      <c r="W24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
+      <c r="W24" s="3" t="n"/>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="Z24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -3729,42 +3904,44 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4255
+          <t xml:space="preserve">4555
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">177
+</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">5248
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1842
+          <t xml:space="preserve">1142
 </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">61
+</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -3781,57 +3958,66 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="n"/>
+          <t xml:space="preserve">1218
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1400
+          <t xml:space="preserve">400
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11140
+          <t xml:space="preserve">1040
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>42</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="n"/>
+          <t xml:space="preserve">11480
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">873
+</t>
+        </is>
+      </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">428
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1177
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
@@ -3848,13 +4034,13 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14575
+          <t xml:space="preserve">14114
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11121
+          <t xml:space="preserve">218218280
 </t>
         </is>
       </c>
@@ -3873,7 +4059,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304
+          <t xml:space="preserve">2304
 </t>
         </is>
       </c>
@@ -3885,31 +4071,32 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2225
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">8055
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">73
+</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -3920,26 +4107,31 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="n"/>
+          <t xml:space="preserve">1105
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">8120
 </t>
         </is>
       </c>
@@ -3951,19 +4143,20 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">1293
 </t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1142
 </t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
@@ -3980,27 +4173,31 @@
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="n"/>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2270
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4024,24 +4221,25 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">31 18
+</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
+          <t xml:space="preserve">12356
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
@@ -4051,22 +4249,27 @@
 </t>
         </is>
       </c>
-      <c r="I27" s="3" t="n"/>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1014
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">1679
 </t>
         </is>
       </c>
@@ -4076,7 +4279,12 @@
 </t>
         </is>
       </c>
-      <c r="N27" s="3" t="n"/>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">220
@@ -4097,10 +4305,16 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="n"/>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1160
@@ -4109,31 +4323,32 @@
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1374
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="n"/>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="n"/>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10266
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">18659
 </t>
         </is>
       </c>
@@ -4152,143 +4367,144 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16210
-</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
+          <t xml:space="preserve">352
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">104646
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1816
+</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1004
+</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1420
+</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11010
+</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">321
+</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2681
+</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1277
+</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1133
+</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">186
 </t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1102
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14280
-</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11208
-</t>
-        </is>
-      </c>
-      <c r="Q28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321
-</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="T28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="U28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">434
-</t>
-        </is>
-      </c>
-      <c r="V28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1277
-</t>
-        </is>
-      </c>
-      <c r="W28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1133
-</t>
-        </is>
-      </c>
-      <c r="X28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="Y28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
@@ -4307,7 +4523,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6249
+          <t xml:space="preserve">6248
 </t>
         </is>
       </c>
@@ -4319,13 +4535,13 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">1221
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
@@ -4337,25 +4553,24 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>497</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1008
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -4367,18 +4582,19 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">73
+</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1413
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -4390,7 +4606,7 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3835
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
@@ -4402,7 +4618,8 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>456</t>
+          <t xml:space="preserve">46
+</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
@@ -4411,10 +4628,15 @@
 </t>
         </is>
       </c>
-      <c r="U29" s="3" t="n"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">421
+</t>
+        </is>
+      </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1277
+          <t xml:space="preserve">2757
 </t>
         </is>
       </c>
@@ -4432,13 +4654,13 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30682
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -4457,7 +4679,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27819
+          <t xml:space="preserve">21819
 </t>
         </is>
       </c>
@@ -4469,7 +4691,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7145
+          <t xml:space="preserve">7265
 </t>
         </is>
       </c>
@@ -4481,7 +4703,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871
+          <t xml:space="preserve">1811
 </t>
         </is>
       </c>
@@ -4493,19 +4715,19 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1558
+          <t xml:space="preserve">1398
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
@@ -4517,13 +4739,13 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1306
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
@@ -4541,7 +4763,7 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
+          <t xml:space="preserve">1591
 </t>
         </is>
       </c>
@@ -4551,16 +4773,21 @@
 </t>
         </is>
       </c>
-      <c r="S30" s="3" t="n"/>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">318
+</t>
+        </is>
+      </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">726
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81941
+          <t xml:space="preserve">11941
 </t>
         </is>
       </c>
@@ -4578,12 +4805,21 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
-</t>
-        </is>
-      </c>
-      <c r="Y30" s="3" t="n"/>
-      <c r="Z30" s="3" t="n"/>
+          <t xml:space="preserve">11900
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4599,7 +4835,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2364
+          <t xml:space="preserve">8564
 </t>
         </is>
       </c>
@@ -4611,7 +4847,8 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>489</t>
+          <t xml:space="preserve">149
+</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -4622,8 +4859,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -4644,15 +4880,30 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="n"/>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">015
+</t>
+        </is>
+      </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">164
 </t>
         </is>
       </c>
-      <c r="M31" s="3" t="n"/>
-      <c r="N31" s="3" t="n"/>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110 1
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">465
@@ -4673,14 +4924,18 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
-</t>
-        </is>
-      </c>
-      <c r="S31" s="3" t="n"/>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -4692,25 +4947,25 @@
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2293
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -4735,13 +4990,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0111
-</t>
+          <t>61444</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">338
+          <t xml:space="preserve">3008
 </t>
         </is>
       </c>
@@ -4753,24 +5007,26 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112321
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">621
+</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">942
+</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -4781,22 +5037,28 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">11260
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="n"/>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">390
@@ -4805,34 +5067,49 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="n"/>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">336
+</t>
+        </is>
+      </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1141
 </t>
         </is>
       </c>
-      <c r="S32" s="3" t="n"/>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="U32" s="3" t="n"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">474
+</t>
+        </is>
+      </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1283
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -4842,10 +5119,15 @@
 </t>
         </is>
       </c>
-      <c r="Y32" s="3" t="n"/>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">349
 </t>
         </is>
       </c>
@@ -4864,25 +5146,25 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4487
+          <t xml:space="preserve">6137
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2229
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
@@ -4912,13 +5194,13 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -4930,46 +5212,56 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1410
-</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1128
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="n"/>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="n"/>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1147
 </t>
         </is>
       </c>
-      <c r="S33" s="3" t="n"/>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
-        </is>
-      </c>
-      <c r="U33" s="3" t="n"/>
+          <t xml:space="preserve">302
+</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1834
+</t>
+        </is>
+      </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12180
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">2617
 </t>
         </is>
       </c>
@@ -4981,13 +5273,13 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">14554
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">1039
 </t>
         </is>
       </c>
@@ -5006,8 +5298,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3866
-</t>
+          <t>38463</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -5018,21 +5309,31 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">1056
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
-</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="n"/>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">018
+</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -5050,31 +5351,31 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11160
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129522
+          <t xml:space="preserve">422
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -5086,55 +5387,55 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">1324
 </t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0250
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190
+          <t xml:space="preserve">1890
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1127
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">0118
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">1010
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">18606
 </t>
         </is>
       </c>
@@ -5153,87 +5454,97 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4339
+          <t xml:space="preserve">4399
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">503
+</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1170
+</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1237
+</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1149
+</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1143
+</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">886
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">303
 </t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1170
-</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="n"/>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1133
-</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1285
-</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="n"/>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1240
-</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">303
-</t>
-        </is>
-      </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
@@ -5245,19 +5556,19 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">2111
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -5269,19 +5580,20 @@
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18398
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5309,60 +5621,70 @@
 </t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">112
 </t>
         </is>
       </c>
-      <c r="F36" s="3" t="n"/>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="n"/>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
-</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="n"/>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1940
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -5374,30 +5696,31 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">28221
 </t>
         </is>
       </c>
@@ -5409,19 +5732,19 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188
+          <t xml:space="preserve">14988
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
@@ -5440,12 +5763,13 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>9661</t>
+          <t xml:space="preserve">22166
+</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11816
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -5457,7 +5781,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11102
+          <t xml:space="preserve">110253
 </t>
         </is>
       </c>
@@ -5469,7 +5793,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">358
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -5481,30 +5805,32 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">10180
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>364</t>
+          <t xml:space="preserve">86
+</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">017
+</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
@@ -5515,65 +5841,67 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t xml:space="preserve">5935
+</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1335
+          <t xml:space="preserve">1336
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17826
+          <t xml:space="preserve">726
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1478
+          <t xml:space="preserve">478
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11410
+          <t xml:space="preserve">1516
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11342
+          <t xml:space="preserve">1340
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">870
+</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9498
+          <t xml:space="preserve">498
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">13150
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
@@ -5592,101 +5920,115 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4433
+          <t xml:space="preserve">4733
 </t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>428</t>
+          <t xml:space="preserve">138
+</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1681
+</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1192
+</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1106
+</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">169
 </t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21112
-</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">267
+</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="n"/>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="n"/>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14180
-</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="Q38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1267
-</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1148
-</t>
-        </is>
-      </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>9401</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2269
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -5735,95 +6077,106 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3146
+          <t xml:space="preserve">9146
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">11921
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
+          <t xml:space="preserve">114126
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">12119
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">102101
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>512</t>
+          <t xml:space="preserve">02
+</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15101
+</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1102
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2110
+</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8187
+</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1593
+</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">100
 </t>
         </is>
       </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1132
-</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11102
-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="n"/>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="n"/>
-      <c r="Q39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="R39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="S39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1224
@@ -5832,32 +6185,37 @@
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
-</t>
-        </is>
-      </c>
-      <c r="V39" s="3" t="n"/>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1248
+</t>
+        </is>
+      </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3964
+          <t xml:space="preserve">964
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2266
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
@@ -5876,23 +6234,24 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6171
-</t>
+          <t>64716</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>303</t>
+          <t xml:space="preserve">917
+</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262217
+          <t xml:space="preserve">1227
 </t>
         </is>
       </c>
@@ -5904,25 +6263,25 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1086
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
@@ -5940,7 +6299,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">801
 </t>
         </is>
       </c>
@@ -5964,28 +6323,34 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">87
+</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7942
-</t>
-        </is>
-      </c>
-      <c r="V40" s="3" t="n"/>
+          <t xml:space="preserve">3942
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1847
@@ -5994,19 +6359,19 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
+          <t xml:space="preserve">2161
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81206
+          <t xml:space="preserve">380
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12216
+          <t xml:space="preserve">2216 3
 </t>
         </is>
       </c>
@@ -6031,12 +6396,12 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">1622
 </t>
         </is>
       </c>
@@ -6048,7 +6413,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">116621
 </t>
         </is>
       </c>
@@ -6072,7 +6437,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
@@ -6084,11 +6449,16 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="n"/>
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">490
@@ -6097,7 +6467,7 @@
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
@@ -6109,7 +6479,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -6121,19 +6491,19 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2926
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1275
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -6145,21 +6515,17 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1016
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1288
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18284
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="n"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -6181,47 +6547,49 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t xml:space="preserve">3121
+</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">1120
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t xml:space="preserve">73
+</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -6237,10 +6605,15 @@
 </t>
         </is>
       </c>
-      <c r="N42" s="3" t="n"/>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">95
+</t>
+        </is>
+      </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9209
+          <t xml:space="preserve">500
 </t>
         </is>
       </c>
@@ -6252,30 +6625,31 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>464</t>
+          <t xml:space="preserve">204
+</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -6287,28 +6661,23 @@
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928
-</t>
-        </is>
-      </c>
-      <c r="Z42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="n"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -6324,13 +6693,13 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3540
+          <t xml:space="preserve">2540
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">3056
 </t>
         </is>
       </c>
@@ -6342,7 +6711,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2239
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -6360,18 +6729,19 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t xml:space="preserve">59
+</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6381,23 +6751,33 @@
 </t>
         </is>
       </c>
-      <c r="M43" s="3" t="n"/>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="n"/>
+          <t xml:space="preserve">9216
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
@@ -6409,31 +6789,31 @@
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -6445,13 +6825,13 @@
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19253
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2461
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -6470,7 +6850,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2380
+          <t xml:space="preserve">2280
 </t>
         </is>
       </c>
@@ -6488,7 +6868,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">12229
 </t>
         </is>
       </c>
@@ -6498,29 +6878,40 @@
 </t>
         </is>
       </c>
-      <c r="H44" s="3" t="n"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6561
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909
-</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="n"/>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -6537,13 +6928,13 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -6555,19 +6946,19 @@
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1093
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -6585,7 +6976,7 @@
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
@@ -6597,7 +6988,7 @@
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1824
+          <t xml:space="preserve">11221
 </t>
         </is>
       </c>
@@ -6614,144 +7005,140 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">331029
-</t>
-        </is>
-      </c>
+      <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118715
+          <t xml:space="preserve">15551
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1919
+          <t xml:space="preserve">4119
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11221
+          <t xml:space="preserve">11021
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822246
+          <t xml:space="preserve">3450
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15123
+          <t xml:space="preserve">2263
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18222
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110111
+          <t xml:space="preserve">12919
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18159
-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="n"/>
+          <t xml:space="preserve">801
+</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112265
+          <t xml:space="preserve">1022615
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">9204
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t xml:space="preserve">1284
+</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10218
+          <t xml:space="preserve">0118
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1838
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18369
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88886
+          <t xml:space="preserve">1026
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214621
+          <t xml:space="preserve">1412
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1061
+          <t xml:space="preserve">01010
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10987
+          <t xml:space="preserve">18 8
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12228
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11172
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">12224
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="n"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -6767,13 +7154,13 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518
-</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>996</t>
+          <t xml:space="preserve">706
+</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -6784,25 +7171,26 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">9010
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -6814,20 +7202,25 @@
       <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="n"/>
+          <t xml:space="preserve">1808
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
@@ -6839,13 +7232,13 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1288
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -6857,27 +7250,37 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3908
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="n"/>
-      <c r="W46" s="3" t="n"/>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">848
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1144
+</t>
+        </is>
+      </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/501/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/501/original_transcribed_data.xlsx
@@ -728,19 +728,19 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5628
+          <t xml:space="preserve">5698
 </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">937
 </t>
         </is>
       </c>
@@ -758,7 +758,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -788,13 +788,13 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -812,13 +812,13 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -855,8 +855,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151 27 1
-</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -867,7 +866,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
@@ -879,13 +878,13 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">764
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -897,19 +896,19 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -921,7 +920,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
@@ -957,12 +956,13 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>04449</t>
+          <t xml:space="preserve">122
+</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -986,13 +986,13 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">382
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23048
+          <t xml:space="preserve">3068
 </t>
         </is>
       </c>
@@ -1029,13 +1029,13 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">2231
 </t>
         </is>
       </c>
@@ -1047,79 +1047,79 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1008
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">85
 </t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">327
+</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">122
 </t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21098
-</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">327
-</t>
-        </is>
-      </c>
-      <c r="R6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">0910
 </t>
         </is>
       </c>
@@ -1131,8 +1131,7 @@
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1642
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
@@ -1143,13 +1142,13 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">302
 </t>
         </is>
       </c>
@@ -1198,13 +1197,13 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -1216,7 +1215,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -1228,13 +1227,13 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -1252,31 +1251,30 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">347
 </t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -1288,14 +1286,12 @@
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>863</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
@@ -1306,7 +1302,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1324,7 +1320,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112851
+          <t xml:space="preserve">2851
 </t>
         </is>
       </c>
@@ -1342,7 +1338,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2828
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -1360,25 +1356,25 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0110
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1161
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -1391,7 +1387,7 @@
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
+          <t xml:space="preserve">32620
 </t>
         </is>
       </c>
@@ -1415,7 +1411,7 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
@@ -1433,25 +1429,25 @@
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110982
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -1471,28 +1467,22 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26660
-</t>
+          <t>196565</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1697
+          <t xml:space="preserve">11697
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14134
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">383
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1164
@@ -1501,25 +1491,25 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3291
+          <t xml:space="preserve">391
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6142
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
+          <t xml:space="preserve">1684
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -1531,7 +1521,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
@@ -1549,7 +1539,7 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">487
+          <t xml:space="preserve">497
 </t>
         </is>
       </c>
@@ -1609,7 +1599,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11584
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
@@ -1628,25 +1618,25 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
+          <t xml:space="preserve">5312
 </t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1872
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -1658,8 +1648,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1696,7 +1685,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -1714,7 +1703,7 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -1726,7 +1715,7 @@
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">448
 </t>
         </is>
       </c>
@@ -1744,13 +1733,13 @@
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -1781,8 +1770,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3080
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1793,25 +1781,25 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -1823,7 +1811,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -1835,11 +1823,16 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">614
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="n"/>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1130
@@ -1860,25 +1853,25 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8210
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -1908,24 +1901,19 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
-</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">10217
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -1949,7 +1937,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
@@ -1985,19 +1973,19 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3108
+          <t xml:space="preserve">3118
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -2009,7 +1997,7 @@
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -2027,19 +2015,19 @@
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">1623
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12170
+          <t xml:space="preserve">14170
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18358
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -2070,7 +2058,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1594
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -2082,20 +2070,14 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
-</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="n"/>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -2125,7 +2107,7 @@
       <c r="N13" s="3" t="n"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">8490
 </t>
         </is>
       </c>
@@ -2143,7 +2125,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
@@ -2173,25 +2155,24 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1021
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">088
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2221,7 +2202,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -2233,7 +2214,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -2257,7 +2238,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -2269,13 +2250,13 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -2299,55 +2280,55 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">045
+</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">738
+</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">360
+</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">270
+</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">145
 </t>
         </is>
       </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">360
-</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">270
-</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0808
+          <t xml:space="preserve">10208
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">2312
 </t>
         </is>
       </c>
@@ -2366,29 +2347,28 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2521
+          <t xml:space="preserve">26521
 </t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>731</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
@@ -2424,7 +2404,7 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -2436,7 +2416,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1488
 </t>
         </is>
       </c>
@@ -2448,48 +2428,42 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3120
-</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1145
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">310
+</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="n"/>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">2008
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38208
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>981</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -2510,25 +2484,25 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2371
+          <t xml:space="preserve">2572
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1823916
+          <t xml:space="preserve">82916
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2168
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">11182
 </t>
         </is>
       </c>
@@ -2558,31 +2532,26 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1898
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="n"/>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22120
+          <t xml:space="preserve">22125
 </t>
         </is>
       </c>
@@ -2594,7 +2563,7 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1547
+          <t xml:space="preserve">1847
 </t>
         </is>
       </c>
@@ -2612,25 +2581,25 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1315
+          <t xml:space="preserve">1313
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -2642,7 +2611,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11438
+          <t xml:space="preserve">1458
 </t>
         </is>
       </c>
@@ -2667,31 +2636,30 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3154
+          <t xml:space="preserve">23134
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3819
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22316
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -2713,16 +2681,21 @@
 </t>
         </is>
       </c>
-      <c r="K17" s="3" t="n"/>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">2104
 </t>
         </is>
       </c>
@@ -2734,7 +2707,7 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
+          <t xml:space="preserve">428
 </t>
         </is>
       </c>
@@ -2758,7 +2731,7 @@
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">73
 </t>
         </is>
       </c>
@@ -2770,7 +2743,7 @@
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9816
+          <t xml:space="preserve">9274
 </t>
         </is>
       </c>
@@ -2799,7 +2772,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -2818,7 +2791,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10321
+          <t xml:space="preserve">2321
 </t>
         </is>
       </c>
@@ -2830,7 +2803,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -2839,26 +2812,21 @@
 </t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
-      </c>
+      <c r="G18" s="3" t="n"/>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -2881,7 +2849,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -2899,13 +2867,13 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2804
+          <t xml:space="preserve">2806
 </t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -2917,7 +2885,7 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
@@ -2929,7 +2897,7 @@
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1081
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
@@ -2941,19 +2909,19 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">2928
 </t>
         </is>
       </c>
@@ -2972,18 +2940,19 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">354
+          <t xml:space="preserve">334
 </t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -3004,15 +2973,10 @@
 </t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
+      <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11206
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -3024,8 +2988,7 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>635</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -3036,7 +2999,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
@@ -3066,7 +3029,7 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
@@ -3078,14 +3041,13 @@
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1614
+          <t xml:space="preserve">414
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>969</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
@@ -3102,13 +3064,13 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">2928
 </t>
         </is>
       </c>
@@ -3127,26 +3089,23 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93905
-</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -3157,7 +3116,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9149
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -3169,7 +3128,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>84</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -3180,7 +3139,7 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
@@ -3192,13 +3151,13 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">550
 </t>
         </is>
       </c>
@@ -3228,8 +3187,7 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>448</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
@@ -3240,25 +3198,25 @@
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16202
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -3283,25 +3241,25 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422
+          <t xml:space="preserve">0422
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">1864
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -3319,7 +3277,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
@@ -3331,13 +3289,13 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">1757
 </t>
         </is>
       </c>
@@ -3403,7 +3361,7 @@
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -3415,13 +3373,13 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2176
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -3440,7 +3398,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5363
+          <t xml:space="preserve">9363
 </t>
         </is>
       </c>
@@ -3458,7 +3416,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2125
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -3506,7 +3464,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -3542,13 +3500,13 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">1849
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">2390
 </t>
         </is>
       </c>
@@ -3560,13 +3518,13 @@
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
@@ -3603,30 +3561,31 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
+          <t xml:space="preserve">1603
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
+          <t xml:space="preserve">735
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t xml:space="preserve">11171
+</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1868
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1610
+          <t xml:space="preserve">1600
 </t>
         </is>
       </c>
@@ -3650,7 +3609,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -3662,37 +3621,37 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2720
+          <t xml:space="preserve">12720
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">412
+          <t xml:space="preserve">413
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1344
+          <t xml:space="preserve">2544
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">735
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">566
+          <t xml:space="preserve">3686
 </t>
         </is>
       </c>
@@ -3710,13 +3669,13 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1388
+          <t xml:space="preserve">1386
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1688
+          <t xml:space="preserve">688
 </t>
         </is>
       </c>
@@ -3734,7 +3693,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11274
+          <t xml:space="preserve">11224
 </t>
         </is>
       </c>
@@ -3753,12 +3712,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
@@ -3770,7 +3729,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">2234
 </t>
         </is>
       </c>
@@ -3782,7 +3741,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">1022
 </t>
         </is>
       </c>
@@ -3794,16 +3753,11 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1174
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -3812,19 +3766,19 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">046
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">346
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -3836,7 +3790,7 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -3854,7 +3808,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -3870,7 +3824,11 @@
 </t>
         </is>
       </c>
-      <c r="W24" s="3" t="n"/>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">86
@@ -3879,13 +3837,13 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -3922,7 +3880,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5248
+          <t xml:space="preserve">10248
 </t>
         </is>
       </c>
@@ -3964,42 +3922,43 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">400
+          <t xml:space="preserve">4010
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">294
+</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11480
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">873
+          <t xml:space="preserve">8373
 </t>
         </is>
       </c>
@@ -4011,18 +3970,18 @@
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>37</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -4034,13 +3993,12 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14114
-</t>
+          <t>416</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218218280
+          <t xml:space="preserve">11121
 </t>
         </is>
       </c>
@@ -4059,7 +4017,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2304
+          <t xml:space="preserve">5304
 </t>
         </is>
       </c>
@@ -4083,7 +4041,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8055
+          <t xml:space="preserve">855
 </t>
         </is>
       </c>
@@ -4131,7 +4089,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8120
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -4143,13 +4101,12 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1293
-</t>
+          <t>993</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -4161,7 +4118,7 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
@@ -4173,13 +4130,13 @@
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -4191,13 +4148,13 @@
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">0220
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4215,13 +4172,13 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5501
+          <t xml:space="preserve">501
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31 18
+          <t xml:space="preserve">318 4
 </t>
         </is>
       </c>
@@ -4233,13 +4190,13 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12356
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -4257,7 +4214,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1014
+          <t xml:space="preserve">1104
 </t>
         </is>
       </c>
@@ -4269,7 +4226,7 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1679
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
@@ -4281,19 +4238,19 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
@@ -4317,23 +4274,27 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">3174
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="n"/>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">96
@@ -4342,13 +4303,12 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18659
+          <t xml:space="preserve">1965
 </t>
         </is>
       </c>
@@ -4367,36 +4327,37 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t xml:space="preserve">16210
+</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">352
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104646
+          <t xml:space="preserve">1376
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1816
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
+          <t xml:space="preserve">1104
 </t>
         </is>
       </c>
@@ -4438,20 +4399,19 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1420
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11010
+          <t xml:space="preserve">1100
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
@@ -4462,19 +4422,19 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2681
+          <t xml:space="preserve">434
 </t>
         </is>
       </c>
@@ -4486,7 +4446,7 @@
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -4502,12 +4462,7 @@
 </t>
         </is>
       </c>
-      <c r="Z28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">908
-</t>
-        </is>
-      </c>
+      <c r="Z28" s="3" t="n"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -4535,13 +4490,13 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
@@ -4559,18 +4514,18 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>493</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">81811
 </t>
         </is>
       </c>
@@ -4594,19 +4549,19 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">413
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">835
 </t>
         </is>
       </c>
@@ -4630,13 +4585,13 @@
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">421
+          <t xml:space="preserve">471
 </t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2757
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
@@ -4648,19 +4603,19 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">230090
 </t>
         </is>
       </c>
@@ -4679,19 +4634,19 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21819
+          <t xml:space="preserve">22819
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1616
+          <t xml:space="preserve">15616
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7265
+          <t xml:space="preserve">7145
 </t>
         </is>
       </c>
@@ -4703,13 +4658,13 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1570
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -4721,7 +4676,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1398
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -4757,20 +4712,19 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
+          <t xml:space="preserve">917
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1591
+          <t xml:space="preserve">1551
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">709
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -4781,13 +4735,13 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11941
+          <t xml:space="preserve">1941
 </t>
         </is>
       </c>
@@ -4805,19 +4759,19 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11900
+          <t xml:space="preserve">1100
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">1069
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4835,7 +4789,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8564
+          <t xml:space="preserve">2364
 </t>
         </is>
       </c>
@@ -4859,7 +4813,8 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -4876,13 +4831,13 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">015
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -4930,7 +4885,8 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">69
+</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
@@ -4990,13 +4946,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>611</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3008
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -5013,19 +4968,19 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">621
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -5037,19 +4992,19 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11260
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -5067,7 +5022,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -5079,7 +5034,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -5103,7 +5058,7 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">1283
 </t>
         </is>
       </c>
@@ -5115,7 +5070,7 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
@@ -5127,7 +5082,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">349
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -5146,7 +5101,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6137
+          <t xml:space="preserve">1225
 </t>
         </is>
       </c>
@@ -5158,7 +5113,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
@@ -5170,7 +5125,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1167
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -5182,7 +5137,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -5194,7 +5149,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -5218,11 +5173,16 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="n"/>
+          <t xml:space="preserve">410
+</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">260
@@ -5231,7 +5191,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -5243,25 +5203,25 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
+          <t xml:space="preserve">1934
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2617
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -5273,14 +5233,13 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14554
+          <t xml:space="preserve">1492
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1039
-</t>
+          <t>432</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5298,7 +5257,8 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>38463</t>
+          <t xml:space="preserve">3866
+</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -5321,121 +5281,121 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1814
+</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="T34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">018
 </t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1172
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">422
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
-      <c r="Q34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="R34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1324
-</t>
-        </is>
-      </c>
-      <c r="S34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="T34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="U34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="V34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1890
-</t>
-        </is>
-      </c>
-      <c r="W34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="X34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0118
-</t>
-        </is>
-      </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18606
+          <t xml:space="preserve">180 16
 </t>
         </is>
       </c>
@@ -5466,13 +5426,13 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -5484,7 +5444,7 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -5496,13 +5456,13 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
@@ -5520,7 +5480,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -5532,19 +5492,14 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
-</t>
-        </is>
-      </c>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">303
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">986
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="n"/>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -5562,7 +5517,7 @@
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2111
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
@@ -5586,16 +5541,11 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="Z35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">21215
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="n"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -5630,34 +5580,23 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="n"/>
+      <c r="K36" s="3" t="n"/>
       <c r="L36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">178
@@ -5672,13 +5611,13 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -5708,7 +5647,7 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -5720,7 +5659,7 @@
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28221
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
@@ -5738,13 +5677,13 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14988
+          <t xml:space="preserve">11860
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
@@ -5769,7 +5708,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">118106
 </t>
         </is>
       </c>
@@ -5781,7 +5720,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110253
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
@@ -5793,7 +5732,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">338
 </t>
         </is>
       </c>
@@ -5805,31 +5744,31 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10180
+          <t xml:space="preserve">1800
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">032
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
@@ -5841,31 +5780,31 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5935
+          <t xml:space="preserve">893
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1336
+          <t xml:space="preserve">133 5
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">726
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">478
+          <t xml:space="preserve">1478
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1516
+          <t xml:space="preserve">11510
 </t>
         </is>
       </c>
@@ -5877,13 +5816,13 @@
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">670
 </t>
         </is>
       </c>
@@ -5895,13 +5834,13 @@
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13150
+          <t xml:space="preserve">11812
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
@@ -5920,13 +5859,13 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4733
+          <t xml:space="preserve">4422
 </t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">2303
 </t>
         </is>
       </c>
@@ -5944,13 +5883,13 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1681
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -5968,7 +5907,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
@@ -5980,31 +5919,31 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
@@ -6016,7 +5955,7 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -6028,7 +5967,7 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -6083,25 +6022,24 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11921
-</t>
+          <t>794</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114126
+          <t xml:space="preserve">1416
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12119
+          <t xml:space="preserve">11866
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102101
+          <t xml:space="preserve">108110
 </t>
         </is>
       </c>
@@ -6113,13 +6051,13 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -6131,25 +6069,24 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15101
+          <t xml:space="preserve">1151
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2110
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -6161,13 +6098,13 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8187
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1593
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -6179,19 +6116,19 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">0294
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -6203,13 +6140,13 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">964
+          <t xml:space="preserve">364
 </t>
         </is>
       </c>
@@ -6234,12 +6171,12 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>64716</t>
+          <t>6414</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
+          <t xml:space="preserve">907
 </t>
         </is>
       </c>
@@ -6251,7 +6188,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -6263,13 +6200,13 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -6281,7 +6218,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -6299,7 +6236,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -6323,7 +6260,7 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
@@ -6341,7 +6278,7 @@
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3942
+          <t xml:space="preserve">842
 </t>
         </is>
       </c>
@@ -6353,26 +6290,25 @@
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1847
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216 3
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6396,12 +6332,13 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t xml:space="preserve">314
+</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1622
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -6413,19 +6350,19 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116621
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -6437,7 +6374,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6461,13 +6398,13 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
@@ -6491,13 +6428,13 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
@@ -6509,7 +6446,7 @@
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -6519,13 +6456,12 @@
 </t>
         </is>
       </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18284
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="n"/>
+      <c r="Y41" s="3" t="n"/>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -6547,37 +6483,37 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3121
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -6595,7 +6531,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
@@ -6607,13 +6543,13 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -6625,7 +6561,7 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
@@ -6637,13 +6573,13 @@
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -6661,19 +6597,19 @@
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -6693,13 +6629,13 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2540
+          <t xml:space="preserve">5340
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3056
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
@@ -6723,7 +6659,7 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">1834
 </t>
         </is>
       </c>
@@ -6753,19 +6689,19 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9216
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -6783,7 +6719,7 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -6801,7 +6737,7 @@
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -6813,7 +6749,7 @@
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -6831,7 +6767,7 @@
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
@@ -6862,13 +6798,13 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12229
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -6898,7 +6834,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -6910,19 +6846,18 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1440
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -6940,25 +6875,25 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
+          <t xml:space="preserve">1123
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">3228
 </t>
         </is>
       </c>
@@ -6970,28 +6905,22 @@
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="Z44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11221
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">508
+</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -7005,58 +6934,63 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n"/>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18011
+</t>
+        </is>
+      </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15551
+          <t xml:space="preserve">1851
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4119
+          <t xml:space="preserve">917
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11021
+          <t xml:space="preserve">11221
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450
+          <t xml:space="preserve">7211
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2263
+          <t xml:space="preserve">523
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">1812
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12919
+          <t xml:space="preserve">12818
 </t>
         </is>
       </c>
@@ -7068,73 +7002,68 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022615
+          <t xml:space="preserve">12265
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9204
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1284
+          <t xml:space="preserve">1700
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0118
+          <t xml:space="preserve">0815
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">1800
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
-</t>
-        </is>
-      </c>
-      <c r="U45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1026
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1264
+</t>
+        </is>
+      </c>
+      <c r="U45" s="3" t="n"/>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412
+          <t xml:space="preserve">1442
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01010
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 8
+          <t xml:space="preserve">1 1
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12224
+          <t xml:space="preserve">12229
 </t>
         </is>
       </c>
@@ -7154,30 +7083,30 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">706
+          <t xml:space="preserve">406
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9010
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -7189,7 +7118,7 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -7199,7 +7128,12 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="n"/>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
@@ -7220,7 +7154,7 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">494
 </t>
         </is>
       </c>
@@ -7238,7 +7172,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -7256,19 +7190,19 @@
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
@@ -7280,13 +7214,13 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">1126
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/501/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/501/original_transcribed_data.xlsx
@@ -740,7 +740,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">937
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -758,7 +758,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -776,7 +776,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -794,13 +794,13 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">345
+          <t xml:space="preserve">355
 </t>
         </is>
       </c>
@@ -812,19 +812,19 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -855,7 +855,8 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t xml:space="preserve">5127
+</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -866,19 +867,19 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
@@ -902,7 +903,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">008
 </t>
         </is>
       </c>
@@ -914,19 +915,14 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
+          <t xml:space="preserve">1360
 </t>
         </is>
       </c>
@@ -944,7 +940,7 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1840
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -956,37 +952,37 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1468
+</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">968
 </t>
         </is>
       </c>
@@ -1011,7 +1007,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3068
+          <t xml:space="preserve">5048
 </t>
         </is>
       </c>
@@ -1035,7 +1031,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2231
+          <t xml:space="preserve">20239
 </t>
         </is>
       </c>
@@ -1047,7 +1043,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -1059,13 +1055,13 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1075,21 +1071,16 @@
 </t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+      <c r="N6" s="3" t="n"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1008
+          <t xml:space="preserve">1400
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -1101,13 +1092,13 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">1152
 </t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
@@ -1119,7 +1110,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0910
+          <t xml:space="preserve">410
 </t>
         </is>
       </c>
@@ -1131,7 +1122,8 @@
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">142
+</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
@@ -1148,7 +1140,7 @@
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">2302
 </t>
         </is>
       </c>
@@ -1173,13 +1165,12 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">353
-</t>
+          <t>353</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -1191,13 +1182,13 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -1215,7 +1206,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -1227,13 +1218,13 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -1257,52 +1248,56 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t xml:space="preserve">1138
+</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">424
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">135
+</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>863</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">334
+</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1320,13 +1315,13 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2851
+          <t xml:space="preserve">4851
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">344
 </t>
         </is>
       </c>
@@ -1350,44 +1345,44 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32620
+          <t xml:space="preserve">362
 </t>
         </is>
       </c>
@@ -1417,41 +1412,45 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">291
+</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1133
+</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">143
 </t>
         </is>
       </c>
-      <c r="U8" s="3" t="inlineStr">
+      <c r="Y8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">422
 </t>
         </is>
       </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="n"/>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1467,22 +1466,28 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>196565</t>
+          <t xml:space="preserve">26361
+</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11697
+          <t xml:space="preserve">1697
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">383
-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n"/>
+          <t xml:space="preserve">1233
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11134
+</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1164
@@ -1497,25 +1502,25 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">442
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1684
+          <t xml:space="preserve">684
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">671
+          <t xml:space="preserve">1671
 </t>
         </is>
       </c>
@@ -1527,37 +1532,37 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1830
+          <t xml:space="preserve">11830
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">497
+          <t xml:space="preserve">487
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">1650
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">1718
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">1277
 </t>
         </is>
       </c>
@@ -1569,7 +1574,7 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12241
+          <t xml:space="preserve">2248
 </t>
         </is>
       </c>
@@ -1587,13 +1592,13 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11862
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -1630,25 +1635,26 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">1232
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">1478
+</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1685,7 +1691,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -1727,25 +1733,25 @@
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">389
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">11062
+</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -1770,7 +1776,8 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>305</t>
+          <t xml:space="preserve">308
+</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1781,7 +1788,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">838
 </t>
         </is>
       </c>
@@ -1799,19 +1806,19 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1469
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -1835,7 +1842,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -1853,7 +1860,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -1865,18 +1872,27 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="n"/>
-      <c r="W11" s="3" t="n"/>
+          <t xml:space="preserve">1310
+</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1140
+</t>
+        </is>
+      </c>
       <c r="X11" s="3" t="n"/>
       <c r="Y11" s="3" t="n"/>
       <c r="Z11" s="3" t="n"/>
@@ -1901,19 +1917,19 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>311</t>
         </is>
       </c>
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10217
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
@@ -1937,7 +1953,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1955,7 +1971,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -1967,25 +1983,24 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3118
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -1997,37 +2012,37 @@
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1840
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1623
+          <t xml:space="preserve">1023
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14170
+          <t xml:space="preserve">470
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -2058,8 +2073,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>424</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -2074,10 +2088,16 @@
 </t>
         </is>
       </c>
-      <c r="H13" s="3" t="n"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1114
+</t>
+        </is>
+      </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t xml:space="preserve">94
+</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -2107,7 +2127,7 @@
       <c r="N13" s="3" t="n"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8490
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
@@ -2125,7 +2145,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
@@ -2143,7 +2163,7 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">440
+          <t xml:space="preserve">4490
 </t>
         </is>
       </c>
@@ -2167,12 +2187,14 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">288
+</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t xml:space="preserve">254
+</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2190,7 +2212,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4890
+          <t xml:space="preserve">4880
 </t>
         </is>
       </c>
@@ -2202,7 +2224,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
@@ -2238,7 +2260,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2250,19 +2272,14 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1220
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="n"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">495
 </t>
         </is>
       </c>
@@ -2274,19 +2291,19 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">2303
 </t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">045
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">738
+          <t xml:space="preserve">73
 </t>
         </is>
       </c>
@@ -2298,7 +2315,7 @@
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
+          <t xml:space="preserve">12360
 </t>
         </is>
       </c>
@@ -2316,19 +2333,19 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10208
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -2347,23 +2364,26 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26521
+          <t xml:space="preserve">5529
 </t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>313</t>
+          <t xml:space="preserve">315
+</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">150
+</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>731</t>
+          <t xml:space="preserve">1231
+</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -2404,19 +2424,14 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1104
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="n"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1488
+          <t xml:space="preserve">4180
 </t>
         </is>
       </c>
@@ -2428,47 +2443,64 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="n"/>
+          <t xml:space="preserve">2310
+</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1145
+</t>
+        </is>
+      </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">1154
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">380
+</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>981</t>
+          <t xml:space="preserve">271
+</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="Y15" s="3" t="n"/>
-      <c r="Z15" s="3" t="n"/>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>10</t>
@@ -2484,25 +2516,25 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2572
+          <t xml:space="preserve">2377
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82916
+          <t xml:space="preserve">129 16
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">768
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11182
+          <t xml:space="preserve">21182
 </t>
         </is>
       </c>
@@ -2514,19 +2546,19 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">973
+          <t xml:space="preserve">3973
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">562
+          <t xml:space="preserve">1362
 </t>
         </is>
       </c>
@@ -2536,22 +2568,27 @@
 </t>
         </is>
       </c>
-      <c r="L16" s="3" t="n"/>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8809
+</t>
+        </is>
+      </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">521
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22125
+          <t xml:space="preserve">2125
 </t>
         </is>
       </c>
@@ -2563,13 +2600,13 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1847
+          <t xml:space="preserve">1547
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">1736
 </t>
         </is>
       </c>
@@ -2581,13 +2618,13 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">1882
 </t>
         </is>
       </c>
@@ -2599,7 +2636,7 @@
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -2611,13 +2648,13 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1458
+          <t xml:space="preserve">11458
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10244
+          <t xml:space="preserve">12244
 </t>
         </is>
       </c>
@@ -2636,19 +2673,20 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23134
+          <t xml:space="preserve">3154
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t xml:space="preserve">134
+</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -2659,7 +2697,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
@@ -2671,7 +2709,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
@@ -2683,7 +2721,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -2695,19 +2733,19 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2104
+          <t xml:space="preserve">1104
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">425
 </t>
         </is>
       </c>
@@ -2737,24 +2775,25 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9274
+          <t xml:space="preserve">376
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>9465</t>
+          <t xml:space="preserve">263
+</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
@@ -2772,7 +2811,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -2791,44 +2830,47 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2321
+          <t xml:space="preserve">2521
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0229
+          <t xml:space="preserve">529
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">1124
+</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">827
-</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="n"/>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>154</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -2837,25 +2879,25 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">1375
 </t>
         </is>
       </c>
@@ -2867,7 +2909,7 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2806
+          <t xml:space="preserve">8291
 </t>
         </is>
       </c>
@@ -2885,31 +2927,31 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">1155
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">404
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">1844
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -2921,7 +2963,7 @@
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2928
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -2940,7 +2982,8 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t xml:space="preserve">3264
+</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2973,10 +3016,15 @@
 </t>
         </is>
       </c>
-      <c r="I19" s="3" t="n"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1206
 </t>
         </is>
       </c>
@@ -2988,7 +3036,8 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>635</t>
+          <t xml:space="preserve">135
+</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -3005,7 +3054,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
+          <t xml:space="preserve">1605
 </t>
         </is>
       </c>
@@ -3023,7 +3072,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -3047,7 +3096,8 @@
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t>969</t>
+          <t xml:space="preserve">1269
+</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
@@ -3058,19 +3108,19 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2928
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -3089,23 +3139,24 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>343</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -3128,12 +3179,13 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">84
+</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -3151,7 +3203,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -3187,7 +3239,8 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>448</t>
+          <t xml:space="preserve">225
+</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
@@ -3198,13 +3251,13 @@
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
@@ -3216,7 +3269,7 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
@@ -3253,13 +3306,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1864
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -3271,7 +3324,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -3289,19 +3342,19 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1757
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -3313,7 +3366,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">420
 </t>
         </is>
       </c>
@@ -3343,7 +3396,7 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
@@ -3355,13 +3408,13 @@
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2863
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -3379,8 +3432,7 @@
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>446</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3398,7 +3450,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9363
+          <t xml:space="preserve">5363
 </t>
         </is>
       </c>
@@ -3440,13 +3492,13 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">020
 </t>
         </is>
       </c>
@@ -3458,22 +3510,17 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">510
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">9
+</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="n"/>
       <c r="P22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">92
@@ -3500,7 +3547,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
@@ -3512,20 +3559,19 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -3567,13 +3613,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">735
+          <t xml:space="preserve">725
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11171
+          <t xml:space="preserve">1171
 </t>
         </is>
       </c>
@@ -3609,7 +3655,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">791
 </t>
         </is>
       </c>
@@ -3621,37 +3667,32 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12720
+          <t xml:space="preserve">2720
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">413
+          <t xml:space="preserve">412
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2544
-</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1544
+</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="n"/>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3686
+          <t xml:space="preserve">366
 </t>
         </is>
       </c>
@@ -3669,19 +3710,19 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1386
+          <t xml:space="preserve">1305
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
+          <t xml:space="preserve">1688
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">1428
 </t>
         </is>
       </c>
@@ -3693,7 +3734,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11224
+          <t xml:space="preserve">1274
 </t>
         </is>
       </c>
@@ -3712,7 +3753,8 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>5035</t>
+          <t xml:space="preserve">5095
+</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3723,62 +3765,67 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1
 </t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2234
-</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1022
-</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1174
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">2946
 </t>
         </is>
       </c>
@@ -3790,7 +3837,7 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
@@ -3826,7 +3873,8 @@
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">138
+</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
@@ -3862,7 +3910,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4555
+          <t xml:space="preserve">455
 </t>
         </is>
       </c>
@@ -3874,131 +3922,133 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1248
+</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1142
+</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1118
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">400
+</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1262
+</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">177
 </t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10248
-</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1142
-</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61
-</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1109
-</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1118
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4010
-</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1140
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1148
-</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8373
-</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1222
-</t>
-        </is>
-      </c>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1328
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">92
 </t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11121
+          <t xml:space="preserve">4573
 </t>
         </is>
       </c>
@@ -4029,25 +4079,25 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -4071,13 +4121,13 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -4101,7 +4151,8 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>993</t>
+          <t xml:space="preserve">293
+</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
@@ -4124,13 +4175,13 @@
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
+          <t xml:space="preserve">1334
 </t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
@@ -4142,19 +4193,20 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0220
+          <t xml:space="preserve">2220
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">250
+</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4172,13 +4224,13 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">501
+          <t xml:space="preserve">5501
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318 4
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
@@ -4208,13 +4260,13 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -4238,19 +4290,19 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -4262,53 +4314,55 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3174
+          <t xml:space="preserve">374
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">148
+</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t xml:space="preserve">1266
+</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1965
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
@@ -4327,7 +4381,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16210
+          <t xml:space="preserve">6210
 </t>
         </is>
       </c>
@@ -4339,25 +4393,25 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1376
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -4369,13 +4423,13 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4393,13 +4447,13 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">420
 </t>
         </is>
       </c>
@@ -4411,7 +4465,8 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t xml:space="preserve">321
+</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
@@ -4422,25 +4477,25 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">5984
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">434
+          <t xml:space="preserve">934
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1277
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
@@ -4452,7 +4507,7 @@
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -4462,7 +4517,11 @@
 </t>
         </is>
       </c>
-      <c r="Z28" s="3" t="n"/>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -4478,7 +4537,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6248
+          <t xml:space="preserve">6249
 </t>
         </is>
       </c>
@@ -4496,7 +4555,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">2383
 </t>
         </is>
       </c>
@@ -4520,12 +4579,13 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>493</t>
+          <t xml:space="preserve">127
+</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81811
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4561,7 +4621,7 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
@@ -4585,7 +4645,7 @@
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">471
+          <t xml:space="preserve">1471
 </t>
         </is>
       </c>
@@ -4597,8 +4657,7 @@
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
@@ -4615,7 +4674,7 @@
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230090
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
@@ -4634,19 +4693,19 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22819
+          <t xml:space="preserve">27819
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15616
+          <t xml:space="preserve">1616
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7145
+          <t xml:space="preserve">745
 </t>
         </is>
       </c>
@@ -4664,25 +4723,25 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">570
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">2370
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1358
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -4706,7 +4765,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2223
+          <t xml:space="preserve">2323
 </t>
         </is>
       </c>
@@ -4718,24 +4777,25 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1551
+          <t xml:space="preserve">1531
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -4753,25 +4813,20 @@
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1668
-</t>
-        </is>
-      </c>
-      <c r="X30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1100
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">668
+</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="n"/>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1069
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">1229
+</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4789,7 +4844,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2364
+          <t xml:space="preserve">3364
 </t>
         </is>
       </c>
@@ -4831,16 +4886,11 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1112
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">164
@@ -4849,7 +4899,7 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110 1
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
@@ -4867,7 +4917,7 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
@@ -4885,7 +4935,7 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4921,13 +4971,13 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -4946,12 +4996,14 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>611</t>
+          <t xml:space="preserve">2086
+</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>238</t>
+          <t xml:space="preserve">338
+</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4972,12 +5024,7 @@
 </t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
+      <c r="H32" s="3" t="n"/>
       <c r="I32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">92
@@ -4992,13 +5039,13 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
@@ -5010,7 +5057,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -5022,7 +5069,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -5046,43 +5093,36 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">11411
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">474
-</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1283
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="n"/>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>4841</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -5101,7 +5141,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1225
+          <t xml:space="preserve">4437
 </t>
         </is>
       </c>
@@ -5113,7 +5153,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">1143
 </t>
         </is>
       </c>
@@ -5125,7 +5165,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">1167
 </t>
         </is>
       </c>
@@ -5137,7 +5177,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -5155,19 +5195,19 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -5191,7 +5231,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1147
 </t>
         </is>
       </c>
@@ -5209,7 +5249,7 @@
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1934
+          <t xml:space="preserve">1834
 </t>
         </is>
       </c>
@@ -5221,7 +5261,7 @@
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -5233,13 +5273,14 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1492
+          <t xml:space="preserve">14209
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">1139
+</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5269,8 +5310,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1056
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -5281,19 +5321,19 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">1152
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -5317,13 +5357,13 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1814
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -5347,19 +5387,19 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -5371,31 +5411,31 @@
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">018
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180 16
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -5414,13 +5454,13 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4399
+          <t xml:space="preserve">4339
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">503
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
@@ -5438,13 +5478,13 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1133
 </t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
@@ -5456,14 +5496,13 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>471</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
@@ -5480,7 +5519,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5496,16 +5535,21 @@
 </t>
         </is>
       </c>
-      <c r="Q35" s="3" t="n"/>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">308
+</t>
+        </is>
+      </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1589
 </t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -5517,7 +5561,7 @@
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">334
 </t>
         </is>
       </c>
@@ -5541,11 +5585,16 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21215
-</t>
-        </is>
-      </c>
-      <c r="Z35" s="3" t="n"/>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -5567,35 +5616,45 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="n"/>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">1048
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="n"/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
       <c r="K36" s="3" t="n"/>
       <c r="L36" s="3" t="inlineStr">
         <is>
@@ -5617,7 +5676,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
@@ -5641,19 +5700,19 @@
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -5665,25 +5724,25 @@
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1806
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11860
+          <t xml:space="preserve">1466
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
@@ -5708,7 +5767,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118106
+          <t xml:space="preserve">1316
 </t>
         </is>
       </c>
@@ -5720,7 +5779,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
@@ -5732,7 +5791,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">338
+          <t xml:space="preserve">558
 </t>
         </is>
       </c>
@@ -5744,13 +5803,13 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">361
 </t>
         </is>
       </c>
@@ -5762,31 +5821,31 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">032
+          <t xml:space="preserve">1532
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">447
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12402
+          <t xml:space="preserve">24092
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">893
+          <t xml:space="preserve">3595
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133 5
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -5804,7 +5863,7 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11510
+          <t xml:space="preserve">1716
 </t>
         </is>
       </c>
@@ -5816,31 +5875,26 @@
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">11411
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
-</t>
-        </is>
-      </c>
-      <c r="X37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">498
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="n"/>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11812
+          <t xml:space="preserve">1882
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
@@ -5859,19 +5913,19 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4422
+          <t xml:space="preserve">4433
 </t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2303
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
@@ -5883,13 +5937,13 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -5901,19 +5955,14 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
@@ -5925,37 +5974,37 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -5967,13 +6016,13 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">1269
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
@@ -6016,30 +6065,31 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9146
+          <t xml:space="preserve">59146
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>794</t>
+          <t xml:space="preserve">292
+</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11866
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108110
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -6051,37 +6101,38 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
+          <t xml:space="preserve">11580
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t xml:space="preserve">9
+</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -6116,13 +6167,13 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0294
+          <t xml:space="preserve">1294
 </t>
         </is>
       </c>
@@ -6140,7 +6191,7 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -6152,7 +6203,7 @@
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -6171,12 +6222,13 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>6414</t>
+          <t xml:space="preserve">6171
+</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">907
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
@@ -6206,7 +6258,7 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -6218,13 +6270,13 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -6236,13 +6288,13 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
@@ -6260,13 +6312,13 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -6278,13 +6330,13 @@
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">842
+          <t xml:space="preserve">942
 </t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">12680
 </t>
         </is>
       </c>
@@ -6296,19 +6348,20 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">3180
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">2236
+</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6338,25 +6391,24 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">1152
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1530
 </t>
         </is>
       </c>
@@ -6386,19 +6438,19 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
@@ -6428,13 +6480,13 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">2326
 </t>
         </is>
       </c>
@@ -6446,20 +6498,26 @@
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1016
-</t>
-        </is>
-      </c>
-      <c r="Y41" s="3" t="n"/>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1289
+</t>
+        </is>
+      </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">264
+</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6483,7 +6541,7 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">392
 </t>
         </is>
       </c>
@@ -6495,13 +6553,13 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">1233
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
@@ -6519,7 +6577,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -6537,26 +6595,25 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">500
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -6579,7 +6636,7 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">1287
 </t>
         </is>
       </c>
@@ -6591,13 +6648,13 @@
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -6609,11 +6666,16 @@
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="Z42" s="3" t="n"/>
+          <t xml:space="preserve">13920
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -6629,13 +6691,13 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340
+          <t xml:space="preserve">2340
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
@@ -6653,13 +6715,13 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
@@ -6677,7 +6739,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -6695,7 +6757,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -6707,7 +6769,7 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -6731,13 +6793,13 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">2314
 </t>
         </is>
       </c>
@@ -6749,7 +6811,7 @@
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -6767,7 +6829,7 @@
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -6786,7 +6848,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2280
+          <t xml:space="preserve">2580
 </t>
         </is>
       </c>
@@ -6804,7 +6866,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
@@ -6834,7 +6896,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">092
 </t>
         </is>
       </c>
@@ -6846,24 +6908,25 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">6440
 </t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
@@ -6875,7 +6938,7 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -6887,13 +6950,13 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3228
+          <t xml:space="preserve">2328
 </t>
         </is>
       </c>
@@ -6911,16 +6974,22 @@
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">12279
+</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">508
-</t>
-        </is>
-      </c>
-      <c r="Z44" s="3" t="n"/>
+          <t xml:space="preserve">2908
+</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1124
+</t>
+        </is>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -6936,43 +7005,42 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18011
+          <t xml:space="preserve">23122
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1851
+          <t xml:space="preserve">1887
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11221
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">9108
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">71949
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7211
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
@@ -6984,89 +7052,84 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12818
+          <t xml:space="preserve">1019
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
+          <t xml:space="preserve">12029
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12265
+          <t xml:space="preserve">2265
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">29084
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1700
-</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0815
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1780
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="n"/>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
-</t>
-        </is>
-      </c>
-      <c r="U45" s="3" t="n"/>
+          <t xml:space="preserve">1369
+</t>
+        </is>
+      </c>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1826
+</t>
+        </is>
+      </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1442
+          <t xml:space="preserve">1462
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">2862
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 1
-</t>
-        </is>
-      </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12229
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1647
+</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="n"/>
       <c r="Z45" s="3" t="n"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -7083,30 +7146,31 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t xml:space="preserve">5518
+</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">406
+          <t xml:space="preserve">4706
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -7118,7 +7182,7 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -7128,12 +7192,7 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
@@ -7142,19 +7201,19 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">494
+          <t xml:space="preserve">1494
 </t>
         </is>
       </c>
@@ -7172,13 +7231,13 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">1390
 </t>
         </is>
       </c>
@@ -7190,13 +7249,13 @@
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">23908
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">2848
 </t>
         </is>
       </c>
@@ -7208,19 +7267,19 @@
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/501/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/501/original_transcribed_data.xlsx
@@ -728,110 +728,92 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5698
-</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
-</t>
+          <t>335</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">355
-</t>
+          <t>355</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>333</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="U4" s="3" t="n"/>
@@ -855,141 +837,118 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1360
-</t>
+          <t>360</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
-</t>
+          <t>317</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1468
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
-</t>
+          <t>322</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1007,141 +966,118 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5048
-</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">339
-</t>
+          <t>339</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20239
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="N6" s="3" t="n"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1400
-</t>
+          <t>400</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
-</t>
+          <t>327</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
-</t>
+          <t>410</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2302
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1159,8 +1095,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5836
-</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1170,134 +1105,112 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">350
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">347
-</t>
+          <t>347</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">424
-</t>
+          <t>424</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1315,135 +1228,113 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4851
-</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
-</t>
+          <t>344</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">362
-</t>
+          <t>362</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>517</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">422
-</t>
+          <t>422</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
@@ -1466,146 +1357,122 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26361
-</t>
+          <t>26560</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1697
-</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
-</t>
+          <t>533</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11134
-</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
-</t>
+          <t>391</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
-</t>
+          <t>442</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
-</t>
+          <t>684</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1671
-</t>
+          <t>671</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
+          <t>325</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11830
-</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">487
-</t>
+          <t>497</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650
-</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718
-</t>
+          <t>718</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2248
-</t>
+          <t>2241</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
-</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1696
-</t>
+          <t>696</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1623,136 +1490,114 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312
-</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>339</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1478
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="N10" s="3" t="n"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
-</t>
+          <t>366</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">448
-</t>
+          <t>448</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">389
-</t>
+          <t>389</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11062
-</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1770,104 +1615,87 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1469
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -1877,20 +1705,17 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X11" s="3" t="n"/>
@@ -1911,8 +1736,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2067
-</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1923,74 +1747,62 @@
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
-</t>
+          <t>530</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
@@ -2000,50 +1812,42 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
-</t>
+          <t>392</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1023
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2061,14 +1865,12 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6013
-</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">343
-</t>
+          <t>343</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -2078,123 +1880,103 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="N13" s="3" t="n"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
-</t>
+          <t>490</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4490
-</t>
+          <t>440</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2212,141 +1994,118 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4880
-</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="N14" s="3" t="n"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
-</t>
+          <t>495</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12360
-</t>
+          <t>360</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2364,141 +2123,118 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5529
-</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="N15" s="3" t="n"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180
-</t>
+          <t>480</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
-</t>
+          <t>380</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2516,146 +2252,122 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2377
-</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129 16
-</t>
+          <t>159 6</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
-</t>
+          <t>768</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21182
-</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
-</t>
+          <t>828</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
-</t>
+          <t>618</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3973
-</t>
+          <t>353</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1362
-</t>
+          <t>562</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8809
-</t>
+          <t>899</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-</t>
+          <t>521</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2125
-</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">622
-</t>
+          <t>622</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1547
-</t>
+          <t>1547</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1736
-</t>
+          <t>736</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
-</t>
+          <t>364</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
-</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1313
-</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>725</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">483
-</t>
+          <t>483</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11458
-</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12244
-</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2673,146 +2385,122 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
-</t>
+          <t>425</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">376
-</t>
+          <t>376</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2830,141 +2518,118 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2521
-</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
-</t>
+          <t>329</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1375
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8291
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1844
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2982,146 +2647,122 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3264
-</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
-</t>
+          <t>605</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>320</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">414
-</t>
+          <t>414</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3149,134 +2790,112 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>550</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>320</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3294,140 +2913,117 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0422
-</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
-</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
-</t>
+          <t>490</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
-</t>
+          <t>366</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
@@ -3450,123 +3046,103 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5363
-</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">020
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O22" s="3" t="n"/>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2390
-</t>
+          <t>390</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
@@ -3576,14 +3152,12 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3601,141 +3175,118 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25175
-</t>
+          <t>25475</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1603
-</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
-</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
-</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
-</t>
+          <t>868</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>572</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">791
-</t>
+          <t>791</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">503
-</t>
+          <t>503</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2720
-</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">412
-</t>
+          <t>413</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1544
-</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="R23" s="3" t="n"/>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
-</t>
+          <t>366</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
-</t>
+          <t>829</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1872
-</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1305
-</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1688
-</t>
+          <t>688</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
-</t>
+          <t>428</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
-</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1274
-</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3753,146 +3304,122 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5095
-</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2946
-</t>
+          <t>546</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">374
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3910,146 +3437,122 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">455
-</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">400
-</t>
+          <t>400</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4573
-</t>
+          <t>453</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4067,146 +3570,122 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304
-</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1334
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2220
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4224,146 +3703,122 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5501
-</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">374
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4381,140 +3836,117 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6210
-</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5984
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">934
-</t>
+          <t>434</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
@@ -4537,122 +3969,102 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6249
-</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
-</t>
+          <t>344</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2383
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">413
-</t>
+          <t>413</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
-</t>
+          <t>335</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1471
-</t>
+          <t>471</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
@@ -4662,20 +4074,17 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4693,128 +4102,107 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27819
-</t>
+          <t>27819</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1616
-</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">745
-</t>
+          <t>745</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
-</t>
+          <t>871</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">570
-</t>
+          <t>570</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2370
-</t>
+          <t>370</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1358
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>506</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2323
-</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
-</t>
+          <t>517</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
-</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>709</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>726</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1941
-</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
-</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="X30" s="3" t="n"/>
@@ -4825,8 +4213,7 @@
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
-</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4844,141 +4231,118 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3364
-</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
-</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">465
-</t>
+          <t>465</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">388
-</t>
+          <t>388</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4996,105 +4360,88 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2086
-</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">338
-</t>
+          <t>338</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="H32" s="3" t="n"/>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
-</t>
+          <t>390</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">336
-</t>
+          <t>336</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11411
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
@@ -5104,14 +4451,12 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="X32" s="3" t="n"/>
@@ -5122,8 +4467,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -5141,146 +4485,122 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4437
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
-</t>
+          <t>410</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14209
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5298,14 +4618,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3866
-</t>
+          <t>3866</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -5315,128 +4633,107 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>522</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>500</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5454,50 +4751,42 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4339
-</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
@@ -5507,92 +4796,77 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1589
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5610,8 +4884,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3413
-</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -5621,129 +4894,108 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1048
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K36" s="3" t="n"/>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
-</t>
+          <t>540</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
-</t>
+          <t>348</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1806
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1466
-</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5761,141 +5013,118 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22166
-</t>
+          <t>22166</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1316
-</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1689
-</t>
+          <t>689</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
-</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">827
-</t>
+          <t>827</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">558
-</t>
+          <t>558</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>839</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1532
-</t>
+          <t>532</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">447
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24092
-</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3595
-</t>
+          <t>593</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
-</t>
+          <t>726</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1478
-</t>
+          <t>479</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1716
-</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1340
-</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11411
-</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>070</t>
         </is>
       </c>
       <c r="X37" s="3" t="n"/>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
-</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5913,141 +5142,118 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4433
-</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>480</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">374
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -6065,146 +5271,122 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59146
-</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11580
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1294
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
-</t>
+          <t>364</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6222,146 +5404,122 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
-</t>
+          <t>510</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
-</t>
+          <t>342</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12680
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3180
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6379,14 +5537,12 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5875
-</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -6396,128 +5552,107 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1530
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
-</t>
+          <t>490</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6535,80 +5670,67 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4811
-</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">392
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
-</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -6618,62 +5740,52 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13920
-</t>
+          <t>520</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6691,146 +5803,122 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2340
-</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>315</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6848,146 +5936,122 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580
-</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">092
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6440
-</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12279
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2908
-</t>
+          <t>508</t>
         </is>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AA44" s="3" t="inlineStr">
@@ -7005,14 +6069,12 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23122
-</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
-</t>
+          <t>1857</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -7022,111 +6084,93 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9108
-</t>
+          <t>918</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71949
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>350</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">523
-</t>
+          <t>523</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1019
-</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12029
-</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2265
-</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29084
-</t>
+          <t>584</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1780
-</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="R45" s="3" t="n"/>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1369
-</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1826
-</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1462
-</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2862
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1647
-</t>
+          <t>547</t>
         </is>
       </c>
       <c r="Y45" s="3" t="n"/>
@@ -7146,141 +6190,122 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518
-</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4706
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n"/>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
-</t>
+          <t>494</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1390
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23908
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2848
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/501/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/501/original_transcribed_data.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>124</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>350</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>317</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>333</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>163</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -2179,7 +2179,7 @@
       <c r="N15" s="3" t="n"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>262</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>268</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>362</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>41</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2347,12 +2347,12 @@
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>125</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>165</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>76</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>375</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>404</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>67</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>96</t>
         </is>
       </c>
       <c r="O22" s="3" t="n"/>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>222</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>272</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>011</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>135</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>98</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>98</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>320</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>194</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>202</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>62</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>27819</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>358</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>318</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>81</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>62</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
@@ -4337,12 +4337,12 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>273</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>08</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>014</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>2437</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>322</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>300</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>340</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>202</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>358</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>393</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>670</t>
         </is>
       </c>
       <c r="X37" s="3" t="n"/>
@@ -5180,7 +5180,11 @@
           <t>60</t>
         </is>
       </c>
-      <c r="K38" s="3" t="n"/>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
           <t>168</t>
@@ -5193,7 +5197,7 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>92</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
@@ -5223,7 +5227,7 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>303</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
@@ -5331,7 +5335,7 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>310</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -5404,7 +5408,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -5459,7 +5463,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -5592,7 +5596,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>102</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
@@ -5770,12 +5774,12 @@
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>115</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
@@ -5843,7 +5847,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
@@ -5903,7 +5907,7 @@
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
@@ -5976,7 +5980,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>32</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -5991,12 +5995,12 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>181</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>440</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -6021,7 +6025,7 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>193</t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
@@ -6069,7 +6073,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>33122</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6084,7 +6088,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>137</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -6104,7 +6108,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>323</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
@@ -6119,12 +6123,12 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>270</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
@@ -6165,12 +6169,12 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>863</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="Y45" s="3" t="n"/>
@@ -6195,7 +6199,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -6210,7 +6214,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>153</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -6245,7 +6249,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -6290,7 +6294,7 @@
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>124</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
@@ -6300,7 +6304,7 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>311</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/501/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/501/original_transcribed_data.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>123</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1284,7 +1284,7 @@
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>262</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>517</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>199</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -2050,7 +2050,7 @@
       <c r="N14" s="3" t="n"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>165</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -2179,7 +2179,7 @@
       <c r="N15" s="3" t="n"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>480</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>768</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>562</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>725</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>554</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>154</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>78</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>175</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>203</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>98</t>
         </is>
       </c>
       <c r="O22" s="3" t="n"/>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>785</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>690</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>572</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -3230,12 +3230,12 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>2730</t>
+          <t>2720</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>099</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>320</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>91</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>520</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>104</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>94</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>434</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>27819</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>558</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>194</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>68</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>611</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>014</t>
+          <t>004</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>2437</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>422</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>108</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>332</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>341</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>22166</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>558</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>070</t>
         </is>
       </c>
       <c r="X37" s="3" t="n"/>
@@ -5180,11 +5180,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
           <t>168</t>
@@ -5197,7 +5193,7 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>97</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
@@ -5295,7 +5291,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -5330,7 +5326,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>98</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -5463,7 +5459,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>91</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -5493,7 +5489,7 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>195</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
@@ -5596,7 +5592,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
@@ -5646,7 +5642,7 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -5774,12 +5770,12 @@
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>118</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
@@ -5862,7 +5858,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
@@ -5940,7 +5936,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>580</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -5995,7 +5991,7 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
@@ -6025,7 +6021,7 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>198</t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
@@ -6045,7 +6041,7 @@
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>109</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
@@ -6073,7 +6069,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>33122</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6098,7 +6094,7 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>719</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -6108,7 +6104,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>523</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
@@ -6123,12 +6119,12 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>650</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>578</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
@@ -6159,7 +6155,7 @@
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
@@ -6174,7 +6170,7 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>647</t>
         </is>
       </c>
       <c r="Y45" s="3" t="n"/>
@@ -6234,7 +6230,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6249,7 +6245,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>91</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -6294,7 +6290,7 @@
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>144</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
@@ -6304,7 +6300,7 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>211</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
